--- a/Example/Extract Pandat Results/P.xlsx
+++ b/Example/Extract Pandat Results/P.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17868\OneDrive\文档\GitHub\ThermoQ\Example\Extract Pandat Results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E37007F6-D0C7-4A18-852E-3CB67AE70C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -73,12 +67,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -86,15 +80,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -140,25 +127,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +243,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,20 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P122"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
-    <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="8" max="8" width="19.5" customWidth="1"/>
-    <col min="10" max="10" width="19.625" customWidth="1"/>
-    <col min="11" max="11" width="27.25" customWidth="1"/>
-    <col min="12" max="12" width="21.25" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,9 +472,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16">
       <c r="A2">
-        <v>883.46268520000001</v>
+        <v>883.4626852</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -515,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>35.563091299003801</v>
+        <v>35.5630912990038</v>
       </c>
       <c r="E2">
         <v>90</v>
@@ -527,13 +495,13 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>97.232636869999993</v>
+        <v>97.23263686999999</v>
       </c>
       <c r="I2">
-        <v>2.7054875269999998</v>
+        <v>2.705487527</v>
       </c>
       <c r="J2">
-        <v>6.187560458E-2</v>
+        <v>0.06187560458</v>
       </c>
       <c r="K2">
         <v>90</v>
@@ -545,18 +513,18 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>2.0332756770000001E-3</v>
+        <v>0.002033275677</v>
       </c>
       <c r="O2">
-        <v>-1.7695292840000001E-3</v>
+        <v>-0.001769529284</v>
       </c>
       <c r="P2">
-        <v>-2.6374639280000002E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0002637463928</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3">
-        <v>879.56719009999995</v>
+        <v>879.5671900999999</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -565,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>38.614879609234201</v>
+        <v>38.6148796092342</v>
       </c>
       <c r="E3">
         <v>89</v>
@@ -577,10 +545,10 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <v>97.330796160000006</v>
+        <v>97.33079616000001</v>
       </c>
       <c r="I3">
-        <v>2.5423783449999999</v>
+        <v>2.542378345</v>
       </c>
       <c r="J3">
         <v>0.1268254972</v>
@@ -595,18 +563,18 @@
         <v>2</v>
       </c>
       <c r="N3">
-        <v>2.1567607590000002E-3</v>
+        <v>0.002156760759</v>
       </c>
       <c r="O3">
-        <v>-1.671794301E-3</v>
+        <v>-0.001671794301</v>
       </c>
       <c r="P3">
-        <v>-4.8496645829999998E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0004849664583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4">
-        <v>875.52140850000001</v>
+        <v>875.5214085</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -615,7 +583,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>41.852658205977598</v>
+        <v>41.8526582059776</v>
       </c>
       <c r="E4">
         <v>88</v>
@@ -627,13 +595,13 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>97.416751619999999</v>
+        <v>97.41675162</v>
       </c>
       <c r="I4">
-        <v>2.3882199019999999</v>
+        <v>2.388219902</v>
       </c>
       <c r="J4">
-        <v>0.19502847879999999</v>
+        <v>0.1950284788</v>
       </c>
       <c r="K4">
         <v>88</v>
@@ -645,18 +613,18 @@
         <v>3</v>
       </c>
       <c r="N4">
-        <v>2.2491255359999998E-3</v>
+        <v>0.002249125536</v>
       </c>
       <c r="O4">
-        <v>-1.5791587350000001E-3</v>
+        <v>-0.001579158735</v>
       </c>
       <c r="P4">
-        <v>-6.6996680049999997E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0006699668005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5">
-        <v>871.31919489999996</v>
+        <v>871.3191949</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -665,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>45.299579143309103</v>
+        <v>45.2995791433091</v>
       </c>
       <c r="E5">
         <v>87</v>
@@ -680,10 +648,10 @@
         <v>97.49100722</v>
       </c>
       <c r="I5">
-        <v>2.2423312640000002</v>
+        <v>2.242331264</v>
       </c>
       <c r="J5">
-        <v>0.26666151399999999</v>
+        <v>0.266661514</v>
       </c>
       <c r="K5">
         <v>87</v>
@@ -695,18 +663,18 @@
         <v>4</v>
       </c>
       <c r="N5">
-        <v>2.3148242739999998E-3</v>
+        <v>0.002314824274</v>
       </c>
       <c r="O5">
-        <v>-1.491053367E-3</v>
+        <v>-0.001491053367</v>
       </c>
       <c r="P5">
-        <v>-8.2377090780000003E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0008237709078</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6">
-        <v>866.95563730000003</v>
+        <v>866.9556373</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -727,13 +695,13 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>97.553992489999999</v>
+        <v>97.55399249</v>
       </c>
       <c r="I6">
         <v>2.104107248</v>
       </c>
       <c r="J6">
-        <v>0.34190026220000003</v>
+        <v>0.3419002622</v>
       </c>
       <c r="K6">
         <v>86</v>
@@ -745,16 +713,16 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>2.3579373569999999E-3</v>
+        <v>0.002357937357</v>
       </c>
       <c r="O6">
-        <v>-1.407301095E-3</v>
+        <v>-0.001407301095</v>
       </c>
       <c r="P6">
-        <v>-9.5063626149999997E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0009506362615</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>862.4269693</v>
       </c>
@@ -765,7 +733,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>52.882603702174301</v>
+        <v>52.8826037021743</v>
       </c>
       <c r="E7">
         <v>85</v>
@@ -777,13 +745,13 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>97.606069739999995</v>
+        <v>97.60606974</v>
       </c>
       <c r="I7">
-        <v>1.9730107219999999</v>
+        <v>1.973010722</v>
       </c>
       <c r="J7">
-        <v>0.42091953669999999</v>
+        <v>0.4209195367</v>
       </c>
       <c r="K7">
         <v>85</v>
@@ -795,18 +763,18 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>2.3821948369999999E-3</v>
+        <v>0.002382194837</v>
       </c>
       <c r="O7">
-        <v>-1.3278963830000001E-3</v>
+        <v>-0.001327896383</v>
       </c>
       <c r="P7">
-        <v>-1.0542984550000001E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001054298455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8">
-        <v>857.73048949999998</v>
+        <v>857.7304895</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -815,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>57.035938375012599</v>
+        <v>57.0359383750126</v>
       </c>
       <c r="E8">
         <v>84</v>
@@ -827,13 +795,13 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>97.647540719999995</v>
+        <v>97.64754071999999</v>
       </c>
       <c r="I8">
         <v>1.848565579</v>
       </c>
       <c r="J8">
-        <v>0.50389369640000004</v>
+        <v>0.5038936964</v>
       </c>
       <c r="K8">
         <v>84</v>
@@ -845,18 +813,18 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>2.390947225E-3</v>
+        <v>0.002390947225</v>
       </c>
       <c r="O8">
-        <v>-1.2528729440000001E-3</v>
+        <v>-0.001252872944</v>
       </c>
       <c r="P8">
-        <v>-1.1380742809999999E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001138074281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9">
-        <v>852.86448900000005</v>
+        <v>852.864489</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -865,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>61.433920588876802</v>
+        <v>61.4339205888768</v>
       </c>
       <c r="E9">
         <v>83</v>
@@ -877,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>97.678652729999996</v>
+        <v>97.67865273</v>
       </c>
       <c r="I9">
         <v>1.730350302</v>
@@ -895,18 +863,18 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>2.3872284569999998E-3</v>
+        <v>0.002387228457</v>
       </c>
       <c r="O9">
-        <v>-1.1822802410000001E-3</v>
+        <v>-0.001182280241</v>
       </c>
       <c r="P9">
-        <v>-1.204948216E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001204948216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10">
-        <v>847.82818459999999</v>
+        <v>847.8281846</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -927,13 +895,13 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>97.699604039999997</v>
+        <v>97.69960404</v>
       </c>
       <c r="I10">
-        <v>1.6179922259999999</v>
+        <v>1.617992226</v>
       </c>
       <c r="J10">
-        <v>0.68240373009999999</v>
+        <v>0.6824037301</v>
       </c>
       <c r="K10">
         <v>82</v>
@@ -945,18 +913,18 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>2.373699198E-3</v>
+        <v>0.002373699198</v>
       </c>
       <c r="O10">
-        <v>-1.116121392E-3</v>
+        <v>-0.001116121392</v>
       </c>
       <c r="P10">
-        <v>-1.257577805E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001257577805</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11">
-        <v>842.62165909999999</v>
+        <v>842.6216591</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -965,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>70.956460973633696</v>
+        <v>70.9564609736337</v>
       </c>
       <c r="E11">
         <v>81</v>
@@ -977,13 +945,13 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>97.710549110000002</v>
+        <v>97.71054911</v>
       </c>
       <c r="I11">
-        <v>1.5111621820000001</v>
+        <v>1.511162182</v>
       </c>
       <c r="J11">
-        <v>0.77828870920000004</v>
+        <v>0.7782887092</v>
       </c>
       <c r="K11">
         <v>81</v>
@@ -995,18 +963,18 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>2.3526602099999999E-3</v>
+        <v>0.00235266021</v>
       </c>
       <c r="O11">
-        <v>-1.0543469619999999E-3</v>
+        <v>-0.001054346962</v>
       </c>
       <c r="P11">
-        <v>-1.298313248E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001298313248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12">
-        <v>869.42539639999995</v>
+        <v>869.4253964</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1015,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>62.111898646200402</v>
+        <v>62.1118986462004</v>
       </c>
       <c r="E12">
         <v>90</v>
@@ -1027,13 +995,13 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>98.701406149999997</v>
+        <v>98.70140615</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>1.2985938459999999</v>
+        <v>1.298593846</v>
       </c>
       <c r="K12">
         <v>90</v>
@@ -1045,15 +1013,15 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>1.399667546E-3</v>
+        <v>0.001399667546</v>
       </c>
       <c r="P12">
-        <v>-1.399667546E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001399667546</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13">
-        <v>881.84275100000002</v>
+        <v>881.842751</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1074,10 +1042,10 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>96.791677320000005</v>
+        <v>96.79167732000001</v>
       </c>
       <c r="I13">
-        <v>3.2083226800000002</v>
+        <v>3.20832268</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1092,15 +1060,15 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1.848691915E-3</v>
+        <v>0.001848691915</v>
       </c>
       <c r="O13">
-        <v>-1.848691915E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001848691915</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14">
-        <v>878.34710719999998</v>
+        <v>878.3471072</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1109,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>39.335391107592997</v>
+        <v>39.335391107593</v>
       </c>
       <c r="E14">
         <v>89</v>
@@ -1121,13 +1089,13 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>96.928328480000005</v>
+        <v>96.92832848</v>
       </c>
       <c r="I14">
-        <v>3.0143230710000002</v>
+        <v>3.014323071</v>
       </c>
       <c r="J14">
-        <v>5.7348449070000002E-2</v>
+        <v>0.05734844907</v>
       </c>
       <c r="K14">
         <v>89</v>
@@ -1139,18 +1107,18 @@
         <v>1</v>
       </c>
       <c r="N14">
-        <v>2.0150068519999998E-3</v>
+        <v>0.002015006852</v>
       </c>
       <c r="O14">
-        <v>-1.77541539E-3</v>
+        <v>-0.00177541539</v>
       </c>
       <c r="P14">
-        <v>-2.395914618E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0002395914618</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15">
-        <v>874.70413959999996</v>
+        <v>874.7041396</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1159,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>42.092875927172003</v>
+        <v>42.092875927172</v>
       </c>
       <c r="E15">
         <v>88</v>
@@ -1171,10 +1139,10 @@
         <v>2</v>
       </c>
       <c r="H15">
-        <v>97.050798850000007</v>
+        <v>97.05079885000001</v>
       </c>
       <c r="I15">
-        <v>2.8314575350000002</v>
+        <v>2.831457535</v>
       </c>
       <c r="J15">
         <v>0.117743614</v>
@@ -1189,18 +1157,18 @@
         <v>2</v>
       </c>
       <c r="N15">
-        <v>2.1494611980000002E-3</v>
+        <v>0.002149461198</v>
       </c>
       <c r="O15">
-        <v>-1.702428649E-3</v>
+        <v>-0.001702428649</v>
       </c>
       <c r="P15">
-        <v>-4.470325493E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0004470325493</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16">
-        <v>870.90632340000002</v>
+        <v>870.9063234</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1221,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="H16">
-        <v>97.159813569999997</v>
+        <v>97.15981357</v>
       </c>
       <c r="I16">
-        <v>2.6588305860000001</v>
+        <v>2.658830586</v>
       </c>
       <c r="J16">
-        <v>0.18135584560000001</v>
+        <v>0.1813558456</v>
       </c>
       <c r="K16">
         <v>87</v>
@@ -1239,18 +1207,18 @@
         <v>3</v>
       </c>
       <c r="N16">
-        <v>2.2550777030000001E-3</v>
+        <v>0.002255077703</v>
       </c>
       <c r="O16">
-        <v>-1.6294321150000001E-3</v>
+        <v>-0.001629432115</v>
       </c>
       <c r="P16">
-        <v>-6.2564558809999999E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0006256455881</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17">
-        <v>866.94755550000002</v>
+        <v>866.9475555</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1271,13 +1239,13 @@
         <v>4</v>
       </c>
       <c r="H17">
-        <v>97.255999540000005</v>
+        <v>97.25599954</v>
       </c>
       <c r="I17">
-        <v>2.4956468680000001</v>
+        <v>2.495646868</v>
       </c>
       <c r="J17">
-        <v>0.24835358799999999</v>
+        <v>0.248353588</v>
       </c>
       <c r="K17">
         <v>86</v>
@@ -1289,18 +1257,18 @@
         <v>4</v>
       </c>
       <c r="N17">
-        <v>2.334838026E-3</v>
+        <v>0.002334838026</v>
       </c>
       <c r="O17">
-        <v>-1.55661665E-3</v>
+        <v>-0.00155661665</v>
       </c>
       <c r="P17">
-        <v>-7.7822137620000003E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0007782213762</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18">
-        <v>862.82304060000001</v>
+        <v>862.8230406</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1309,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>51.561910780659602</v>
+        <v>51.5619107806596</v>
       </c>
       <c r="E18">
         <v>85</v>
@@ -1321,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>97.339895420000005</v>
+        <v>97.33989542</v>
       </c>
       <c r="I18">
         <v>2.341200706</v>
@@ -1339,18 +1307,18 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>2.3917901239999999E-3</v>
+        <v>0.002391790124</v>
       </c>
       <c r="O18">
-        <v>-1.4844607659999999E-3</v>
+        <v>-0.001484460766</v>
       </c>
       <c r="P18">
-        <v>-9.0732935780000004E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0009073293578</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19">
-        <v>858.52918980000004</v>
+        <v>858.5291898</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1359,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>55.178514144170599</v>
+        <v>55.1785141441706</v>
       </c>
       <c r="E19">
         <v>84</v>
@@ -1371,13 +1339,13 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>97.411960629999996</v>
+        <v>97.41196063</v>
       </c>
       <c r="I19">
         <v>2.194866647</v>
       </c>
       <c r="J19">
-        <v>0.39317272180000001</v>
+        <v>0.3931727218</v>
       </c>
       <c r="K19">
         <v>84</v>
@@ -1389,18 +1357,18 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>2.4289579779999998E-3</v>
+        <v>0.002428957978</v>
       </c>
       <c r="O19">
-        <v>-1.4135310119999999E-3</v>
+        <v>-0.001413531012</v>
       </c>
       <c r="P19">
-        <v>-1.0154269660000001E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001015426966</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20">
-        <v>854.06352890000005</v>
+        <v>854.0635289000001</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1409,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>59.040879453251101</v>
+        <v>59.0408794532511</v>
       </c>
       <c r="E20">
         <v>83</v>
@@ -1421,13 +1389,13 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>97.472583580000006</v>
+        <v>97.47258358000001</v>
       </c>
       <c r="I20">
-        <v>2.0560908879999999</v>
+        <v>2.056090888</v>
       </c>
       <c r="J20">
-        <v>0.47132553300000002</v>
+        <v>0.471325533</v>
       </c>
       <c r="K20">
         <v>83</v>
@@ -1439,18 +1407,18 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>2.4493200860000001E-3</v>
+        <v>0.002449320086</v>
       </c>
       <c r="O20">
-        <v>-1.3444104239999999E-3</v>
+        <v>-0.001344410424</v>
       </c>
       <c r="P20">
-        <v>-1.104909662E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001104909662</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21">
-        <v>849.42461639999999</v>
+        <v>849.4246164</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1459,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>63.157427266000298</v>
+        <v>63.1574272660003</v>
       </c>
       <c r="E21">
         <v>82</v>
@@ -1471,13 +1439,13 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>97.522089109999996</v>
+        <v>97.52208911</v>
       </c>
       <c r="I21">
-        <v>1.9243835439999999</v>
+        <v>1.924383544</v>
       </c>
       <c r="J21">
-        <v>0.55352734349999999</v>
+        <v>0.5535273435</v>
       </c>
       <c r="K21">
         <v>82</v>
@@ -1489,18 +1457,18 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>2.455701935E-3</v>
+        <v>0.002455701935</v>
       </c>
       <c r="O21">
-        <v>-1.277615261E-3</v>
+        <v>-0.001277615261</v>
       </c>
       <c r="P21">
-        <v>-1.178086674E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001178086674</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22">
-        <v>844.61196829999994</v>
+        <v>844.6119682999999</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1509,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>67.512760683767993</v>
+        <v>67.51276068376799</v>
       </c>
       <c r="E22">
         <v>81</v>
@@ -1521,13 +1489,13 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>97.560745319999995</v>
+        <v>97.56074532</v>
       </c>
       <c r="I22">
-        <v>1.7993115989999999</v>
+        <v>1.799311599</v>
       </c>
       <c r="J22">
-        <v>0.63994307750000001</v>
+        <v>0.6399430775</v>
       </c>
       <c r="K22">
         <v>81</v>
@@ -1539,18 +1507,18 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>2.450722718E-3</v>
+        <v>0.002450722718</v>
       </c>
       <c r="O22">
-        <v>-1.213568414E-3</v>
+        <v>-0.001213568414</v>
       </c>
       <c r="P22">
-        <v>-1.2371543039999999E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001237154304</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23">
-        <v>928.40929500000004</v>
+        <v>928.409295</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1571,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>99.676685840000005</v>
+        <v>99.67668584</v>
       </c>
       <c r="I23">
-        <v>0.32331416079999997</v>
+        <v>0.3233141608</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1589,15 +1557,15 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>1.9773210130000001E-3</v>
+        <v>0.001977321013</v>
       </c>
       <c r="O23">
-        <v>-1.9773210130000001E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001977321013</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24">
-        <v>839.62599079999995</v>
+        <v>839.6259908</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1606,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>72.105911076743993</v>
+        <v>72.10591107674399</v>
       </c>
       <c r="E24">
         <v>80</v>
@@ -1618,13 +1586,13 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>97.588769690000007</v>
+        <v>97.58876969000001</v>
       </c>
       <c r="I24">
         <v>1.680492581</v>
       </c>
       <c r="J24">
-        <v>0.73073772979999996</v>
+        <v>0.7307377298</v>
       </c>
       <c r="K24">
         <v>80</v>
@@ -1636,18 +1604,18 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>2.4367687469999998E-3</v>
+        <v>0.002436768747</v>
       </c>
       <c r="O24">
-        <v>-1.152595111E-3</v>
+        <v>-0.001152595111</v>
       </c>
       <c r="P24">
-        <v>-1.2841736360000001E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001284173636</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25">
-        <v>922.78200100000004</v>
+        <v>922.782001</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1656,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>8.4518641913977604</v>
+        <v>8.45186419139776</v>
       </c>
       <c r="E25">
         <v>98</v>
@@ -1668,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>99.588018129999995</v>
+        <v>99.58801812999999</v>
       </c>
       <c r="I25">
         <v>0.3056516816</v>
@@ -1686,18 +1654,18 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>1.8796785879999999E-3</v>
+        <v>0.001879678588</v>
       </c>
       <c r="O25">
-        <v>-8.2177673710000004E-4</v>
+        <v>-0.0008217767371</v>
       </c>
       <c r="P25">
-        <v>-1.057901851E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001057901851</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26">
-        <v>917.04304060000004</v>
+        <v>917.0430406</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1718,13 +1686,13 @@
         <v>2</v>
       </c>
       <c r="H26">
-        <v>99.495611249999996</v>
+        <v>99.49561125</v>
       </c>
       <c r="I26">
         <v>0.2887802726</v>
       </c>
       <c r="J26">
-        <v>0.21560847520000001</v>
+        <v>0.2156084752</v>
       </c>
       <c r="K26">
         <v>97</v>
@@ -1736,18 +1704,18 @@
         <v>2</v>
       </c>
       <c r="N26">
-        <v>1.8274334790000001E-3</v>
+        <v>0.001827433479</v>
       </c>
       <c r="O26">
-        <v>-5.2075892039999999E-4</v>
+        <v>-0.0005207589204</v>
       </c>
       <c r="P26">
-        <v>-1.306674559E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001306674559</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27">
-        <v>911.18390399999998</v>
+        <v>911.183904</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1756,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>19.065517783708898</v>
+        <v>19.0655177837089</v>
       </c>
       <c r="E27">
         <v>96</v>
@@ -1768,10 +1736,10 @@
         <v>3</v>
       </c>
       <c r="H27">
-        <v>99.399213939999996</v>
+        <v>99.39921394</v>
       </c>
       <c r="I27">
-        <v>0.27264697539999999</v>
+        <v>0.2726469754</v>
       </c>
       <c r="J27">
         <v>0.3281390797</v>
@@ -1786,18 +1754,18 @@
         <v>3</v>
       </c>
       <c r="N27">
-        <v>1.782882753E-3</v>
+        <v>0.001782882753</v>
       </c>
       <c r="O27">
-        <v>-3.8147934959999999E-4</v>
+        <v>-0.0003814793496</v>
       </c>
       <c r="P27">
-        <v>-1.401403403E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001401403403</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28">
-        <v>905.19682339999997</v>
+        <v>905.1968234</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1806,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>24.689142261447302</v>
+        <v>24.6891422614473</v>
       </c>
       <c r="E28">
         <v>95</v>
@@ -1818,13 +1786,13 @@
         <v>4</v>
       </c>
       <c r="H28">
-        <v>99.298570929999997</v>
+        <v>99.29857093</v>
       </c>
       <c r="I28">
-        <v>0.25720404359999999</v>
+        <v>0.2572040436</v>
       </c>
       <c r="J28">
-        <v>0.44422502609999998</v>
+        <v>0.4442250261</v>
       </c>
       <c r="K28">
         <v>95</v>
@@ -1836,16 +1804,16 @@
         <v>4</v>
       </c>
       <c r="N28">
-        <v>1.7407898799999999E-3</v>
+        <v>0.00174078988</v>
       </c>
       <c r="O28">
-        <v>-3.0080262149999998E-4</v>
+        <v>-0.0003008026215</v>
       </c>
       <c r="P28">
-        <v>-1.439987258E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001439987258</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29">
         <v>899.0747566</v>
       </c>
@@ -1868,13 +1836,13 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>99.193422130000002</v>
+        <v>99.19342213</v>
       </c>
       <c r="I29">
-        <v>0.24240855580000001</v>
+        <v>0.2424085558</v>
       </c>
       <c r="J29">
-        <v>0.56416931029999995</v>
+        <v>0.5641693102999999</v>
       </c>
       <c r="K29">
         <v>94</v>
@@ -1886,18 +1854,18 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>1.6998590240000001E-3</v>
+        <v>0.001699859024</v>
       </c>
       <c r="O29">
-        <v>-2.4796457940000002E-4</v>
+        <v>-0.0002479645794</v>
       </c>
       <c r="P29">
-        <v>-1.451894444E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001451894444</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30">
-        <v>892.81137139999998</v>
+        <v>892.8113714</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1906,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>36.637289492864397</v>
+        <v>36.6372894928644</v>
       </c>
       <c r="E30">
         <v>93</v>
@@ -1918,13 +1886,13 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>99.083501870000006</v>
+        <v>99.08350187000001</v>
       </c>
       <c r="I30">
-        <v>0.22822212950000001</v>
+        <v>0.2282221295</v>
       </c>
       <c r="J30">
-        <v>0.68827599849999999</v>
+        <v>0.6882759985</v>
       </c>
       <c r="K30">
         <v>93</v>
@@ -1936,18 +1904,18 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>1.6597541600000001E-3</v>
+        <v>0.00165975416</v>
       </c>
       <c r="O30">
-        <v>-2.105626927E-4</v>
+        <v>-0.0002105626927</v>
       </c>
       <c r="P30">
-        <v>-1.4491914669999999E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001449191467</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31">
-        <v>886.40103079999994</v>
+        <v>886.4010307999999</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1956,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>42.980012462514701</v>
+        <v>42.9800124625147</v>
       </c>
       <c r="E31">
         <v>92</v>
@@ -1968,13 +1936,13 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>98.968538069999994</v>
+        <v>98.96853806999999</v>
       </c>
       <c r="I31">
-        <v>0.21461066370000001</v>
+        <v>0.2146106637</v>
       </c>
       <c r="J31">
-        <v>0.81685126519999995</v>
+        <v>0.8168512652</v>
       </c>
       <c r="K31">
         <v>92</v>
@@ -1986,18 +1954,18 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>1.6204437879999999E-3</v>
+        <v>0.001620443788</v>
       </c>
       <c r="O31">
-        <v>-1.8263283990000001E-4</v>
+        <v>-0.0001826328399</v>
       </c>
       <c r="P31">
-        <v>-1.437810948E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001437810948</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32">
-        <v>879.83877889999997</v>
+        <v>879.8387789</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2006,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>49.575984339152697</v>
+        <v>49.5759843391527</v>
       </c>
       <c r="E32">
         <v>91</v>
@@ -2018,10 +1986,10 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>98.848251559999994</v>
+        <v>98.84825155999999</v>
       </c>
       <c r="I32">
-        <v>0.20154407569999999</v>
+        <v>0.2015440757</v>
       </c>
       <c r="J32">
         <v>0.9502043671</v>
@@ -2036,18 +2004,18 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>1.5819993520000001E-3</v>
+        <v>0.001581999352</v>
       </c>
       <c r="O32">
-        <v>-1.609488047E-4</v>
+        <v>-0.0001609488047</v>
       </c>
       <c r="P32">
-        <v>-1.4210505480000001E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001421050548</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33">
-        <v>927.64560359999996</v>
+        <v>927.6456036</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2056,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>5.2180773467317803</v>
+        <v>5.21807734673178</v>
       </c>
       <c r="E33">
         <v>99</v>
@@ -2068,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="H33">
-        <v>99.887132539999996</v>
+        <v>99.88713254</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2086,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="N33">
-        <v>1.7014691639999999E-3</v>
+        <v>0.001701469164</v>
       </c>
       <c r="P33">
-        <v>-1.7014691639999999E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001701469164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34">
         <v>873.1203266</v>
       </c>
@@ -2103,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>56.427444684130997</v>
+        <v>56.427444684131</v>
       </c>
       <c r="E34">
         <v>90</v>
@@ -2115,10 +2083,10 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>98.722355390000004</v>
+        <v>98.72235539</v>
       </c>
       <c r="I34">
-        <v>0.18899604780000001</v>
+        <v>0.1889960478</v>
       </c>
       <c r="J34">
         <v>1.088648565</v>
@@ -2133,18 +2101,18 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>1.544521883E-3</v>
+        <v>0.001544521883</v>
       </c>
       <c r="O34">
-        <v>-1.4361109890000001E-4</v>
+        <v>-0.0001436110989</v>
       </c>
       <c r="P34">
-        <v>-1.4009107839999999E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001400910784</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35">
-        <v>866.24203890000001</v>
+        <v>866.2420389</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2153,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>63.540219250267498</v>
+        <v>63.5402192502675</v>
       </c>
       <c r="E35">
         <v>89</v>
@@ -2165,13 +2133,13 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>98.590554229999995</v>
+        <v>98.59055423</v>
       </c>
       <c r="I35">
-        <v>0.17694377789999999</v>
+        <v>0.1769437779</v>
       </c>
       <c r="J35">
-        <v>1.2325019960000001</v>
+        <v>1.232501996</v>
       </c>
       <c r="K35">
         <v>89</v>
@@ -2183,18 +2151,18 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>1.508112238E-3</v>
+        <v>0.001508112238</v>
       </c>
       <c r="O35">
-        <v>-1.2942708469999999E-4</v>
+        <v>-0.0001294270847</v>
       </c>
       <c r="P35">
-        <v>-1.378685153E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001378685153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36">
-        <v>923.35186620000002</v>
+        <v>923.3518662</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2203,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>6.8668334032638096</v>
+        <v>6.86683340326381</v>
       </c>
       <c r="E36">
         <v>98</v>
@@ -2215,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>99.356663670000003</v>
+        <v>99.35666367</v>
       </c>
       <c r="I36">
-        <v>0.64333632529999996</v>
+        <v>0.6433363253</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2233,15 +2201,15 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>1.9765734049999998E-3</v>
+        <v>0.001976573405</v>
       </c>
       <c r="O36">
-        <v>-1.9765734049999998E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001976573405</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37">
-        <v>917.93230630000005</v>
+        <v>917.9323063000001</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2262,13 +2230,13 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>99.292395850000005</v>
+        <v>99.29239585000001</v>
       </c>
       <c r="I37">
-        <v>0.60760821310000002</v>
+        <v>0.6076082131</v>
       </c>
       <c r="J37">
-        <v>9.9995932159999995E-2</v>
+        <v>0.09999593216</v>
       </c>
       <c r="K37">
         <v>97</v>
@@ -2280,16 +2248,16 @@
         <v>1</v>
       </c>
       <c r="N37">
-        <v>1.9632877950000001E-3</v>
+        <v>0.001963287795</v>
       </c>
       <c r="O37">
-        <v>-1.1924182379999999E-3</v>
+        <v>-0.001192418238</v>
       </c>
       <c r="P37">
-        <v>-7.7086955710000001E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0007708695571</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38">
         <v>912.3977036</v>
       </c>
@@ -2300,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>16.670265495370298</v>
+        <v>16.6702654953703</v>
       </c>
       <c r="E38">
         <v>96</v>
@@ -2312,13 +2280,13 @@
         <v>2</v>
       </c>
       <c r="H38">
-        <v>99.223475250000007</v>
+        <v>99.22347525000001</v>
       </c>
       <c r="I38">
-        <v>0.57353880260000001</v>
+        <v>0.5735388026</v>
       </c>
       <c r="J38">
-        <v>0.20298595150000001</v>
+        <v>0.2029859515</v>
       </c>
       <c r="K38">
         <v>96</v>
@@ -2330,18 +2298,18 @@
         <v>2</v>
       </c>
       <c r="N38">
-        <v>1.9338091029999999E-3</v>
+        <v>0.001933809103</v>
       </c>
       <c r="O38">
-        <v>-8.5571261099999995E-4</v>
+        <v>-0.000855712611</v>
       </c>
       <c r="P38">
-        <v>-1.0780964919999999E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001078096492</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39">
-        <v>906.73983239999995</v>
+        <v>906.7398324</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2350,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>21.860070532972401</v>
+        <v>21.8600705329724</v>
       </c>
       <c r="E39">
         <v>95</v>
@@ -2362,13 +2330,13 @@
         <v>3</v>
       </c>
       <c r="H39">
-        <v>99.149733220000002</v>
+        <v>99.14973322</v>
       </c>
       <c r="I39">
-        <v>0.54101522629999999</v>
+        <v>0.5410152263</v>
       </c>
       <c r="J39">
-        <v>0.30925155589999997</v>
+        <v>0.3092515559</v>
       </c>
       <c r="K39">
         <v>95</v>
@@ -2380,18 +2348,18 @@
         <v>3</v>
       </c>
       <c r="N39">
-        <v>1.898174942E-3</v>
+        <v>0.001898174942</v>
       </c>
       <c r="O39">
-        <v>-6.6734841570000004E-4</v>
+        <v>-0.0006673484157</v>
       </c>
       <c r="P39">
-        <v>-1.230826527E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001230826527</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40">
-        <v>900.95127419999994</v>
+        <v>900.9512741999999</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2400,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>27.264970723220301</v>
+        <v>27.2649707232203</v>
       </c>
       <c r="E40">
         <v>94</v>
@@ -2412,13 +2380,13 @@
         <v>4</v>
       </c>
       <c r="H40">
-        <v>99.070991250000006</v>
+        <v>99.07099125000001</v>
       </c>
       <c r="I40">
-        <v>0.50993581899999996</v>
+        <v>0.509935819</v>
       </c>
       <c r="J40">
-        <v>0.41907293309999999</v>
+        <v>0.4190729331</v>
       </c>
       <c r="K40">
         <v>94</v>
@@ -2430,18 +2398,18 @@
         <v>4</v>
       </c>
       <c r="N40">
-        <v>1.8595025289999999E-3</v>
+        <v>0.001859502529</v>
       </c>
       <c r="O40">
-        <v>-5.4638690759999998E-4</v>
+        <v>-0.0005463869076</v>
       </c>
       <c r="P40">
-        <v>-1.313115621E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001313115621</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41">
-        <v>895.02539330000002</v>
+        <v>895.0253933</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2450,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>32.898000968937303</v>
+        <v>32.8980009689373</v>
       </c>
       <c r="E41">
         <v>93</v>
@@ -2462,13 +2430,13 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>98.987060720000002</v>
+        <v>98.98706072</v>
       </c>
       <c r="I41">
         <v>0.4802092812</v>
       </c>
       <c r="J41">
-        <v>0.53273000110000002</v>
+        <v>0.5327300011</v>
       </c>
       <c r="K41">
         <v>93</v>
@@ -2480,18 +2448,18 @@
         <v>5</v>
       </c>
       <c r="N41">
-        <v>1.8192706380000001E-3</v>
+        <v>0.001819270638</v>
       </c>
       <c r="O41">
-        <v>-4.6180961049999998E-4</v>
+        <v>-0.0004618096105</v>
       </c>
       <c r="P41">
-        <v>-1.357461027E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001357461027</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42">
-        <v>888.95631579999997</v>
+        <v>888.9563158</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2500,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>38.768989023953097</v>
+        <v>38.7689890239531</v>
       </c>
       <c r="E42">
         <v>92</v>
@@ -2512,13 +2480,13 @@
         <v>6</v>
       </c>
       <c r="H42">
-        <v>98.897742579999999</v>
+        <v>98.89774258</v>
       </c>
       <c r="I42">
-        <v>0.45175403200000003</v>
+        <v>0.451754032</v>
       </c>
       <c r="J42">
-        <v>0.65050338460000001</v>
+        <v>0.6505033846</v>
       </c>
       <c r="K42">
         <v>92</v>
@@ -2530,18 +2498,18 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>1.7783668249999999E-3</v>
+        <v>0.001778366825</v>
       </c>
       <c r="O42">
-        <v>-3.9916540150000001E-4</v>
+        <v>-0.0003991654015</v>
       </c>
       <c r="P42">
-        <v>-1.3792014240000001E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001379201424</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43">
-        <v>882.73890830000005</v>
+        <v>882.7389083</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2550,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>44.884678511987502</v>
+        <v>44.8846785119875</v>
       </c>
       <c r="E43">
         <v>91</v>
@@ -2562,13 +2530,13 @@
         <v>7</v>
       </c>
       <c r="H43">
-        <v>98.802827160000007</v>
+        <v>98.80282716000001</v>
       </c>
       <c r="I43">
-        <v>0.42449753429999998</v>
+        <v>0.4244975343</v>
       </c>
       <c r="J43">
-        <v>0.77267530630000003</v>
+        <v>0.7726753063</v>
       </c>
       <c r="K43">
         <v>91</v>
@@ -2580,18 +2548,18 @@
         <v>7</v>
       </c>
       <c r="N43">
-        <v>1.7373970160000001E-3</v>
+        <v>0.001737397016</v>
       </c>
       <c r="O43">
-        <v>-3.5080600290000001E-4</v>
+        <v>-0.0003508060029</v>
       </c>
       <c r="P43">
-        <v>-1.3865910129999999E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001386591013</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44">
-        <v>921.71268789999999</v>
+        <v>921.7126879</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2612,13 +2580,13 @@
         <v>2</v>
       </c>
       <c r="H44">
-        <v>99.771369710000002</v>
+        <v>99.77136971</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0.22863029030000001</v>
+        <v>0.2286302903</v>
       </c>
       <c r="K44">
         <v>98</v>
@@ -2630,15 +2598,15 @@
         <v>2</v>
       </c>
       <c r="N44">
-        <v>1.6693868719999999E-3</v>
+        <v>0.001669386872</v>
       </c>
       <c r="P44">
-        <v>-1.6693868719999999E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001669386872</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45">
-        <v>876.36875850000001</v>
+        <v>876.3687585</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2647,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>51.248856335889897</v>
+        <v>51.2488563358899</v>
       </c>
       <c r="E45">
         <v>90</v>
@@ -2659,13 +2627,13 @@
         <v>8</v>
       </c>
       <c r="H45">
-        <v>98.702093860000005</v>
+        <v>98.70209386000001</v>
       </c>
       <c r="I45">
-        <v>0.39837570300000003</v>
+        <v>0.398375703</v>
       </c>
       <c r="J45">
-        <v>0.89953043629999996</v>
+        <v>0.8995304363</v>
       </c>
       <c r="K45">
         <v>90</v>
@@ -2677,18 +2645,18 @@
         <v>8</v>
       </c>
       <c r="N45">
-        <v>1.696802515E-3</v>
+        <v>0.001696802515</v>
       </c>
       <c r="O45">
-        <v>-3.122990667E-4</v>
+        <v>-0.0003122990667</v>
       </c>
       <c r="P45">
-        <v>-1.384503449E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001384503449</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46">
-        <v>869.84215610000001</v>
+        <v>869.8421561</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2697,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>57.862454304989797</v>
+        <v>57.8624543049898</v>
       </c>
       <c r="E46">
         <v>89</v>
@@ -2709,13 +2677,13 @@
         <v>9</v>
       </c>
       <c r="H46">
-        <v>98.595311039999999</v>
+        <v>98.59531104</v>
       </c>
       <c r="I46">
         <v>0.3733322892</v>
       </c>
       <c r="J46">
-        <v>1.0313566670000001</v>
+        <v>1.031356667</v>
       </c>
       <c r="K46">
         <v>89</v>
@@ -2727,18 +2695,18 @@
         <v>9</v>
       </c>
       <c r="N46">
-        <v>1.656915204E-3</v>
+        <v>0.001656915204</v>
       </c>
       <c r="O46">
-        <v>-2.8089487E-4</v>
+        <v>-0.00028089487</v>
       </c>
       <c r="P46">
-        <v>-1.3760203339999999E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001376020334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47">
-        <v>863.15607450000005</v>
+        <v>863.1560745</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2747,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>64.730018014885701</v>
+        <v>64.7300180148857</v>
       </c>
       <c r="E47">
         <v>88</v>
@@ -2759,7 +2727,7 @@
         <v>10</v>
       </c>
       <c r="H47">
-        <v>98.482235840000001</v>
+        <v>98.48223584</v>
       </c>
       <c r="I47">
         <v>0.3493183077</v>
@@ -2777,18 +2745,18 @@
         <v>10</v>
       </c>
       <c r="N47">
-        <v>1.6179865410000001E-3</v>
+        <v>0.001617986541</v>
       </c>
       <c r="O47">
-        <v>-2.5479388919999999E-4</v>
+        <v>-0.0002547938892</v>
       </c>
       <c r="P47">
-        <v>-1.363192652E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001363192652</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48">
-        <v>918.28735500000005</v>
+        <v>918.287355</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2809,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>99.038839339999996</v>
+        <v>99.03883934</v>
       </c>
       <c r="I48">
-        <v>0.96116065750000002</v>
+        <v>0.9611606575</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -2827,15 +2795,15 @@
         <v>0</v>
       </c>
       <c r="N48">
-        <v>1.9717974779999998E-3</v>
+        <v>0.001971797478</v>
       </c>
       <c r="O48">
-        <v>-1.9717974779999998E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001971797478</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49">
-        <v>913.08507410000004</v>
+        <v>913.0850741</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2844,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>14.918765035879799</v>
+        <v>14.9187650358798</v>
       </c>
       <c r="E49">
         <v>96</v>
@@ -2856,13 +2824,13 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>98.999145949999999</v>
+        <v>98.99914595</v>
       </c>
       <c r="I49">
-        <v>0.90698034530000005</v>
+        <v>0.9069803453</v>
       </c>
       <c r="J49">
-        <v>9.3873703629999999E-2</v>
+        <v>0.09387370363</v>
       </c>
       <c r="K49">
         <v>96</v>
@@ -2874,18 +2842,18 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>2.0105905030000002E-3</v>
+        <v>0.002010590503</v>
       </c>
       <c r="O49">
-        <v>-1.4030794110000001E-3</v>
+        <v>-0.001403079411</v>
       </c>
       <c r="P49">
-        <v>-6.0751109199999999E-4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.000607511092</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50">
-        <v>907.76423639999996</v>
+        <v>907.7642364</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2906,13 +2874,13 @@
         <v>2</v>
       </c>
       <c r="H50">
-        <v>98.953819240000001</v>
+        <v>98.95381924</v>
       </c>
       <c r="I50">
-        <v>0.85540076379999996</v>
+        <v>0.8554007638</v>
       </c>
       <c r="J50">
-        <v>0.19077999579999999</v>
+        <v>0.1907799958</v>
       </c>
       <c r="K50">
         <v>95</v>
@@ -2924,16 +2892,16 @@
         <v>2</v>
       </c>
       <c r="N50">
-        <v>2.0099317659999999E-3</v>
+        <v>0.002009931766</v>
       </c>
       <c r="O50">
-        <v>-1.090172154E-3</v>
+        <v>-0.001090172154</v>
       </c>
       <c r="P50">
-        <v>-9.1975961159999995E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0009197596115999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51">
         <v>902.3168531</v>
       </c>
@@ -2956,10 +2924,10 @@
         <v>3</v>
       </c>
       <c r="H51">
-        <v>98.902778339999998</v>
+        <v>98.90277834</v>
       </c>
       <c r="I51">
-        <v>0.80624169180000005</v>
+        <v>0.8062416918</v>
       </c>
       <c r="J51">
         <v>0.2909799703</v>
@@ -2974,18 +2942,18 @@
         <v>3</v>
       </c>
       <c r="N51">
-        <v>1.9910332859999999E-3</v>
+        <v>0.001991033286</v>
       </c>
       <c r="O51">
-        <v>-8.9086847949999999E-4</v>
+        <v>-0.0008908684795</v>
       </c>
       <c r="P51">
-        <v>-1.1001648070000001E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001100164807</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52">
-        <v>896.73580819999995</v>
+        <v>896.7358082</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2994,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>29.784531200855501</v>
+        <v>29.7845312008555</v>
       </c>
       <c r="E52">
         <v>93</v>
@@ -3009,10 +2977,10 @@
         <v>98.84592576</v>
       </c>
       <c r="I52">
-        <v>0.75934092310000001</v>
+        <v>0.7593409231</v>
       </c>
       <c r="J52">
-        <v>0.39473331709999998</v>
+        <v>0.3947333171</v>
       </c>
       <c r="K52">
         <v>93</v>
@@ -3024,18 +2992,18 @@
         <v>4</v>
       </c>
       <c r="N52">
-        <v>1.9622474710000001E-3</v>
+        <v>0.001962247471</v>
       </c>
       <c r="O52">
-        <v>-7.5208813869999998E-4</v>
+        <v>-0.0007520881387</v>
       </c>
       <c r="P52">
-        <v>-1.2101593319999999E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001210159332</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53">
-        <v>891.01482729999998</v>
+        <v>891.0148273</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3044,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>35.174355115978202</v>
+        <v>35.1743551159782</v>
       </c>
       <c r="E53">
         <v>92</v>
@@ -3056,13 +3024,13 @@
         <v>5</v>
       </c>
       <c r="H53">
-        <v>98.783147720000002</v>
+        <v>98.78314772</v>
       </c>
       <c r="I53">
-        <v>0.71455301500000001</v>
+        <v>0.714553015</v>
       </c>
       <c r="J53">
-        <v>0.50229926189999996</v>
+        <v>0.5022992619</v>
       </c>
       <c r="K53">
         <v>92</v>
@@ -3074,16 +3042,16 @@
         <v>5</v>
       </c>
       <c r="N53">
-        <v>1.927716347E-3</v>
+        <v>0.001927716347</v>
       </c>
       <c r="O53">
-        <v>-6.4949930049999999E-4</v>
+        <v>-0.0006494993005</v>
       </c>
       <c r="P53">
-        <v>-1.2782170469999999E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001278217047</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54">
         <v>885.1484494</v>
       </c>
@@ -3094,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>40.800051924855701</v>
+        <v>40.8000519248557</v>
       </c>
       <c r="E54">
         <v>91</v>
@@ -3106,13 +3074,13 @@
         <v>6</v>
       </c>
       <c r="H54">
-        <v>98.714314549999997</v>
+        <v>98.71431455</v>
       </c>
       <c r="I54">
-        <v>0.67174803240000003</v>
+        <v>0.6717480324</v>
       </c>
       <c r="J54">
-        <v>0.61393741310000005</v>
+        <v>0.6139374131000001</v>
       </c>
       <c r="K54">
         <v>91</v>
@@ -3124,18 +3092,18 @@
         <v>6</v>
       </c>
       <c r="N54">
-        <v>1.889826228E-3</v>
+        <v>0.001889826228</v>
       </c>
       <c r="O54">
-        <v>-5.7036481920000001E-4</v>
+        <v>-0.0005703648192</v>
       </c>
       <c r="P54">
-        <v>-1.319461408E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001319461408</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55">
-        <v>915.66251969999996</v>
+        <v>915.6625197</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -3144,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>16.211384644516599</v>
+        <v>16.2113846445166</v>
       </c>
       <c r="E55">
         <v>97</v>
@@ -3156,13 +3124,13 @@
         <v>3</v>
       </c>
       <c r="H55">
-        <v>99.652382070000002</v>
+        <v>99.65238207</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>0.34761793019999998</v>
+        <v>0.3476179302</v>
       </c>
       <c r="K55">
         <v>97</v>
@@ -3174,15 +3142,15 @@
         <v>3</v>
       </c>
       <c r="N55">
-        <v>1.6362126659999999E-3</v>
+        <v>0.001636212666</v>
       </c>
       <c r="P55">
-        <v>-1.6362126659999999E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001636212666</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56">
-        <v>879.13199940000004</v>
+        <v>879.1319994</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -3191,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>46.667673099330997</v>
+        <v>46.667673099331</v>
       </c>
       <c r="E56">
         <v>90</v>
@@ -3203,13 +3171,13 @@
         <v>7</v>
       </c>
       <c r="H56">
-        <v>98.639280979999995</v>
+        <v>98.63928098</v>
       </c>
       <c r="I56">
-        <v>0.63081045670000002</v>
+        <v>0.6308104567</v>
       </c>
       <c r="J56">
-        <v>0.72990856049999997</v>
+        <v>0.7299085605</v>
       </c>
       <c r="K56">
         <v>90</v>
@@ -3221,16 +3189,16 @@
         <v>7</v>
       </c>
       <c r="N56">
-        <v>1.8500950770000001E-3</v>
+        <v>0.001850095077</v>
       </c>
       <c r="O56">
-        <v>-5.0736026719999997E-4</v>
+        <v>-0.0005073602672</v>
       </c>
       <c r="P56">
-        <v>-1.34273481E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.00134273481</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57">
         <v>872.9615622</v>
       </c>
@@ -3241,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>52.780097221646301</v>
+        <v>52.7800972216463</v>
       </c>
       <c r="E57">
         <v>89</v>
@@ -3253,13 +3221,13 @@
         <v>8</v>
       </c>
       <c r="H57">
-        <v>98.557886530000005</v>
+        <v>98.55788653</v>
       </c>
       <c r="I57">
-        <v>0.59163807599999996</v>
+        <v>0.591638076</v>
       </c>
       <c r="J57">
-        <v>0.85047539350000001</v>
+        <v>0.8504753935</v>
       </c>
       <c r="K57">
         <v>89</v>
@@ -3271,18 +3239,18 @@
         <v>8</v>
       </c>
       <c r="N57">
-        <v>1.8095537259999999E-3</v>
+        <v>0.001809553726</v>
       </c>
       <c r="O57">
-        <v>-4.5596666020000001E-4</v>
+        <v>-0.0004559666602</v>
       </c>
       <c r="P57">
-        <v>-1.353587066E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001353587066</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58">
-        <v>866.63395830000002</v>
+        <v>866.6339583</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3303,13 +3271,13 @@
         <v>9</v>
       </c>
       <c r="H58">
-        <v>98.469955870000007</v>
+        <v>98.46995587000001</v>
       </c>
       <c r="I58">
-        <v>0.55414095659999996</v>
+        <v>0.5541409566</v>
       </c>
       <c r="J58">
-        <v>0.97590316840000002</v>
+        <v>0.9759031684</v>
       </c>
       <c r="K58">
         <v>88</v>
@@ -3321,18 +3289,18 @@
         <v>9</v>
       </c>
       <c r="N58">
-        <v>1.768930902E-3</v>
+        <v>0.001768930902</v>
       </c>
       <c r="O58">
-        <v>-4.1323808890000001E-4</v>
+        <v>-0.0004132380889</v>
       </c>
       <c r="P58">
-        <v>-1.3556928129999999E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001355692813</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59">
-        <v>860.14672010000004</v>
+        <v>860.1467201</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3341,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>65.742431199098206</v>
+        <v>65.74243119909821</v>
       </c>
       <c r="E59">
         <v>87</v>
@@ -3353,13 +3321,13 @@
         <v>10</v>
       </c>
       <c r="H59">
-        <v>98.375299229999996</v>
+        <v>98.37529923</v>
       </c>
       <c r="I59">
-        <v>0.51824045090000004</v>
+        <v>0.5182404509</v>
       </c>
       <c r="J59">
-        <v>1.1064603180000001</v>
+        <v>1.106460318</v>
       </c>
       <c r="K59">
         <v>87</v>
@@ -3371,18 +3339,18 @@
         <v>10</v>
       </c>
       <c r="N59">
-        <v>1.7287535640000001E-3</v>
+        <v>0.001728753564</v>
       </c>
       <c r="O59">
-        <v>-3.7716707139999998E-4</v>
+        <v>-0.0003771670714</v>
       </c>
       <c r="P59">
-        <v>-1.3515864920000001E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001351586492</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60">
-        <v>913.20565610000006</v>
+        <v>913.2056561000001</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3391,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>13.867428165920201</v>
+        <v>13.8674281659202</v>
       </c>
       <c r="E60">
         <v>96</v>
@@ -3403,10 +3371,10 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>98.722162229999995</v>
+        <v>98.72216223</v>
       </c>
       <c r="I60">
-        <v>1.2778377670000001</v>
+        <v>1.277837767</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3421,15 +3389,15 @@
         <v>0</v>
       </c>
       <c r="N60">
-        <v>1.9632651880000002E-3</v>
+        <v>0.001963265188</v>
       </c>
       <c r="O60">
-        <v>-1.9632651890000002E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001963265189</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61">
-        <v>908.22921680000002</v>
+        <v>908.2292168</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3438,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>18.188921240652199</v>
+        <v>18.1889212406522</v>
       </c>
       <c r="E61">
         <v>95</v>
@@ -3450,13 +3418,13 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>98.707200589999999</v>
+        <v>98.70720059</v>
       </c>
       <c r="I61">
         <v>1.204828821</v>
       </c>
       <c r="J61">
-        <v>8.7970593139999997E-2</v>
+        <v>0.08797059314</v>
       </c>
       <c r="K61">
         <v>95</v>
@@ -3468,18 +3436,18 @@
         <v>1</v>
       </c>
       <c r="N61">
-        <v>2.03827207E-3</v>
+        <v>0.00203827207</v>
       </c>
       <c r="O61">
-        <v>-1.5367831120000001E-3</v>
+        <v>-0.001536783112</v>
       </c>
       <c r="P61">
-        <v>-5.0148895849999999E-4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0005014889585</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62">
-        <v>903.13055880000002</v>
+        <v>903.1305588</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3488,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>22.684156249610101</v>
+        <v>22.6841562496101</v>
       </c>
       <c r="E62">
         <v>94</v>
@@ -3500,10 +3468,10 @@
         <v>2</v>
       </c>
       <c r="H62">
-        <v>98.685560749999993</v>
+        <v>98.68556074999999</v>
       </c>
       <c r="I62">
-        <v>1.1354351600000001</v>
+        <v>1.13543516</v>
       </c>
       <c r="J62">
         <v>0.1790040863</v>
@@ -3518,18 +3486,18 @@
         <v>2</v>
       </c>
       <c r="N62">
-        <v>2.0654471450000001E-3</v>
+        <v>0.002065447145</v>
       </c>
       <c r="O62">
-        <v>-1.2626969020000001E-3</v>
+        <v>-0.001262696902</v>
       </c>
       <c r="P62">
-        <v>-8.0275024339999999E-4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0008027502434</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63">
-        <v>897.90188279999995</v>
+        <v>897.9018828</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3550,13 +3518,13 @@
         <v>3</v>
       </c>
       <c r="H63">
-        <v>98.657255559999996</v>
+        <v>98.65725556</v>
       </c>
       <c r="I63">
-        <v>1.0694011059999999</v>
+        <v>1.069401106</v>
       </c>
       <c r="J63">
-        <v>0.27334333779999997</v>
+        <v>0.2733433378</v>
       </c>
       <c r="K63">
         <v>93</v>
@@ -3568,18 +3536,18 @@
         <v>3</v>
       </c>
       <c r="N63">
-        <v>2.066248583E-3</v>
+        <v>0.002066248583</v>
       </c>
       <c r="O63">
-        <v>-1.0703445150000001E-3</v>
+        <v>-0.001070344515</v>
       </c>
       <c r="P63">
-        <v>-9.9590406740000001E-4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0009959040674</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64">
-        <v>892.53633090000005</v>
+        <v>892.5363309000001</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -3588,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>32.277417066932102</v>
+        <v>32.2774170669321</v>
       </c>
       <c r="E64">
         <v>92</v>
@@ -3600,13 +3568,13 @@
         <v>4</v>
       </c>
       <c r="H64">
-        <v>98.622273300000003</v>
+        <v>98.6222733</v>
       </c>
       <c r="I64">
-        <v>1.0064969749999999</v>
+        <v>1.006496975</v>
       </c>
       <c r="J64">
-        <v>0.37122972520000003</v>
+        <v>0.3712297252</v>
       </c>
       <c r="K64">
         <v>92</v>
@@ -3618,18 +3586,18 @@
         <v>4</v>
       </c>
       <c r="N64">
-        <v>2.0510814109999998E-3</v>
+        <v>0.002051081411</v>
       </c>
       <c r="O64">
-        <v>-9.2714736320000004E-4</v>
+        <v>-0.0009271473632</v>
       </c>
       <c r="P64">
-        <v>-1.1239340480000001E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001123934048</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
       <c r="A65">
-        <v>887.02794740000002</v>
+        <v>887.0279474</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3650,13 +3618,13 @@
         <v>5</v>
       </c>
       <c r="H65">
-        <v>98.580578979999999</v>
+        <v>98.58057898</v>
       </c>
       <c r="I65">
-        <v>0.94651704049999996</v>
+        <v>0.9465170405</v>
       </c>
       <c r="J65">
-        <v>0.47290398030000003</v>
+        <v>0.4729039803</v>
       </c>
       <c r="K65">
         <v>91</v>
@@ -3668,18 +3636,18 @@
         <v>5</v>
       </c>
       <c r="N65">
-        <v>2.0257729380000001E-3</v>
+        <v>0.002025772938</v>
       </c>
       <c r="O65">
-        <v>-8.1598035759999996E-4</v>
+        <v>-0.0008159803576</v>
       </c>
       <c r="P65">
-        <v>-1.20979258E-3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.00120979258</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66">
-        <v>909.48693390000005</v>
+        <v>909.4869339000001</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3700,13 +3668,13 @@
         <v>4</v>
       </c>
       <c r="H66">
-        <v>99.529841270000006</v>
+        <v>99.52984127000001</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>0.47015873499999999</v>
+        <v>0.470158735</v>
       </c>
       <c r="K66">
         <v>96</v>
@@ -3718,15 +3686,15 @@
         <v>4</v>
       </c>
       <c r="N66">
-        <v>1.602318788E-3</v>
+        <v>0.001602318788</v>
       </c>
       <c r="P66">
-        <v>-1.602318788E-3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001602318788</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
       <c r="A67">
-        <v>881.37164189999999</v>
+        <v>881.3716419</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -3735,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>42.768004116178297</v>
+        <v>42.7680041161783</v>
       </c>
       <c r="E67">
         <v>90</v>
@@ -3747,13 +3715,13 @@
         <v>6</v>
       </c>
       <c r="H67">
-        <v>98.532115340000004</v>
+        <v>98.53211534</v>
       </c>
       <c r="I67">
-        <v>0.88927770419999996</v>
+        <v>0.8892777042</v>
       </c>
       <c r="J67">
-        <v>0.57860695679999996</v>
+        <v>0.5786069568</v>
       </c>
       <c r="K67">
         <v>90</v>
@@ -3765,18 +3733,18 @@
         <v>6</v>
       </c>
       <c r="N67">
-        <v>1.9939309369999998E-3</v>
+        <v>0.001993930937</v>
       </c>
       <c r="O67">
-        <v>-7.2696349719999999E-4</v>
+        <v>-0.0007269634972</v>
       </c>
       <c r="P67">
-        <v>-1.2669674389999999E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001266967439</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
       <c r="A68">
-        <v>875.56315510000002</v>
+        <v>875.5631551</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3785,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>48.370570288341703</v>
+        <v>48.3705702883417</v>
       </c>
       <c r="E68">
         <v>89</v>
@@ -3803,7 +3771,7 @@
         <v>0.8346156991</v>
       </c>
       <c r="J68">
-        <v>0.68858031770000006</v>
+        <v>0.6885803177000001</v>
       </c>
       <c r="K68">
         <v>89</v>
@@ -3815,18 +3783,18 @@
         <v>7</v>
       </c>
       <c r="N68">
-        <v>1.9579493629999999E-3</v>
+        <v>0.001957949363</v>
       </c>
       <c r="O68">
-        <v>-6.5398189280000004E-4</v>
+        <v>-0.0006539818928</v>
       </c>
       <c r="P68">
-        <v>-1.3039674709999999E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001303967471</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
       <c r="A69">
-        <v>869.59902629999999</v>
+        <v>869.5990263</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -3835,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>54.215374999938703</v>
+        <v>54.2153749999387</v>
       </c>
       <c r="E69">
         <v>88</v>
@@ -3847,13 +3815,13 @@
         <v>8</v>
       </c>
       <c r="H69">
-        <v>98.414546360000003</v>
+        <v>98.41454636</v>
       </c>
       <c r="I69">
-        <v>0.78238646830000003</v>
+        <v>0.7823864683</v>
       </c>
       <c r="J69">
-        <v>0.80306717289999996</v>
+        <v>0.8030671729</v>
       </c>
       <c r="K69">
         <v>88</v>
@@ -3865,18 +3833,18 @@
         <v>8</v>
       </c>
       <c r="N69">
-        <v>1.9194932249999999E-3</v>
+        <v>0.001919493225</v>
       </c>
       <c r="O69">
-        <v>-5.9303620380000001E-4</v>
+        <v>-0.0005930362038</v>
       </c>
       <c r="P69">
-        <v>-1.326457021E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001326457021</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
       <c r="A70">
-        <v>863.47656310000002</v>
+        <v>863.4765631</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -3900,10 +3868,10 @@
         <v>98.34522484</v>
       </c>
       <c r="I70">
-        <v>0.73246253750000001</v>
+        <v>0.7324625375</v>
       </c>
       <c r="J70">
-        <v>0.92231262739999997</v>
+        <v>0.9223126274</v>
       </c>
       <c r="K70">
         <v>87</v>
@@ -3915,18 +3883,18 @@
         <v>9</v>
       </c>
       <c r="N70">
-        <v>1.8797469109999999E-3</v>
+        <v>0.001879746911</v>
       </c>
       <c r="O70">
-        <v>-5.4138855110000001E-4</v>
+        <v>-0.0005413885511</v>
       </c>
       <c r="P70">
-        <v>-1.3383583600000001E-3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.00133835836</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
       <c r="A71">
-        <v>857.19381220000002</v>
+        <v>857.1938122</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -3935,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>66.631333708789995</v>
+        <v>66.63133370879</v>
       </c>
       <c r="E71">
         <v>86</v>
@@ -3947,13 +3915,13 @@
         <v>10</v>
       </c>
       <c r="H71">
-        <v>98.268703599999995</v>
+        <v>98.26870359999999</v>
       </c>
       <c r="I71">
-        <v>0.68473208789999995</v>
+        <v>0.6847320879</v>
       </c>
       <c r="J71">
-        <v>1.0465643099999999</v>
+        <v>1.04656431</v>
       </c>
       <c r="K71">
         <v>86</v>
@@ -3965,18 +3933,18 @@
         <v>10</v>
       </c>
       <c r="N71">
-        <v>1.839603657E-3</v>
+        <v>0.001839603657</v>
       </c>
       <c r="O71">
-        <v>-4.9710407549999997E-4</v>
+        <v>-0.0004971040755</v>
       </c>
       <c r="P71">
-        <v>-1.3424995820000001E-3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001342499582</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
       <c r="A72">
-        <v>908.09706310000001</v>
+        <v>908.0970631</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -3985,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>17.455522941986501</v>
+        <v>17.4555229419865</v>
       </c>
       <c r="E72">
         <v>95</v>
@@ -3997,10 +3965,10 @@
         <v>0</v>
       </c>
       <c r="H72">
-        <v>98.405621260000004</v>
+        <v>98.40562126</v>
       </c>
       <c r="I72">
-        <v>1.5943787439999999</v>
+        <v>1.594378744</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4015,15 +3983,15 @@
         <v>0</v>
       </c>
       <c r="N72">
-        <v>1.9511874340000001E-3</v>
+        <v>0.001951187434</v>
       </c>
       <c r="O72">
-        <v>-1.9511874340000001E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001951187434</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73">
-        <v>903.35405089999995</v>
+        <v>903.3540508999999</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -4032,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>21.507048001347201</v>
+        <v>21.5070480013472</v>
       </c>
       <c r="E73">
         <v>94</v>
@@ -4044,13 +4012,13 @@
         <v>1</v>
       </c>
       <c r="H73">
-        <v>98.415538729999994</v>
+        <v>98.41553872999999</v>
       </c>
       <c r="I73">
-        <v>1.5021693460000001</v>
+        <v>1.502169346</v>
       </c>
       <c r="J73">
-        <v>8.2291927289999997E-2</v>
+        <v>0.08229192729</v>
       </c>
       <c r="K73">
         <v>94</v>
@@ -4062,18 +4030,18 @@
         <v>1</v>
       </c>
       <c r="N73">
-        <v>2.0530338680000001E-3</v>
+        <v>0.002053033868</v>
       </c>
       <c r="O73">
-        <v>-1.626306242E-3</v>
+        <v>-0.001626306242</v>
       </c>
       <c r="P73">
-        <v>-4.2672762640000002E-4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0004267276264</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
       <c r="A74">
-        <v>898.48500290000004</v>
+        <v>898.4850029</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -4094,10 +4062,10 @@
         <v>2</v>
       </c>
       <c r="H74">
-        <v>98.417671429999999</v>
+        <v>98.41767143</v>
       </c>
       <c r="I74">
-        <v>1.4146602960000001</v>
+        <v>1.414660296</v>
       </c>
       <c r="J74">
         <v>0.1676682709</v>
@@ -4112,18 +4080,18 @@
         <v>2</v>
       </c>
       <c r="N74">
-        <v>2.105395191E-3</v>
+        <v>0.002105395191</v>
       </c>
       <c r="O74">
-        <v>-1.393290096E-3</v>
+        <v>-0.001393290096</v>
       </c>
       <c r="P74">
-        <v>-7.121050952E-4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0007121050952</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
       <c r="A75">
-        <v>893.48226450000004</v>
+        <v>893.4822645</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -4144,10 +4112,10 @@
         <v>3</v>
       </c>
       <c r="H75">
-        <v>98.412132270000001</v>
+        <v>98.41213227</v>
       </c>
       <c r="I75">
-        <v>1.3315120620000001</v>
+        <v>1.331512062</v>
       </c>
       <c r="J75">
         <v>0.2563556676</v>
@@ -4162,18 +4130,18 @@
         <v>3</v>
       </c>
       <c r="N75">
-        <v>2.1266149299999999E-3</v>
+        <v>0.00212661493</v>
       </c>
       <c r="O75">
-        <v>-1.2166489109999999E-3</v>
+        <v>-0.001216648911</v>
       </c>
       <c r="P75">
-        <v>-9.0996601889999995E-4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0009099660189</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
       <c r="A76">
-        <v>888.33919419999995</v>
+        <v>888.3391942</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -4194,13 +4162,13 @@
         <v>4</v>
       </c>
       <c r="H76">
-        <v>98.399000610000002</v>
+        <v>98.39900061</v>
       </c>
       <c r="I76">
         <v>1.252420187</v>
       </c>
       <c r="J76">
-        <v>0.34857919859999997</v>
+        <v>0.3485791986</v>
       </c>
       <c r="K76">
         <v>91</v>
@@ -4212,18 +4180,18 @@
         <v>4</v>
       </c>
       <c r="N76">
-        <v>2.1271458480000001E-3</v>
+        <v>0.002127145848</v>
       </c>
       <c r="O76">
-        <v>-1.0773801739999999E-3</v>
+        <v>-0.001077380174</v>
       </c>
       <c r="P76">
-        <v>-1.0497656739999999E-3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001049765674</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
       <c r="A77">
-        <v>903.17843370000003</v>
+        <v>903.1784337</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -4232,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>28.075088057426498</v>
+        <v>28.0750880574265</v>
       </c>
       <c r="E77">
         <v>95</v>
@@ -4244,13 +4212,13 @@
         <v>5</v>
       </c>
       <c r="H77">
-        <v>99.403418680000001</v>
+        <v>99.40341868</v>
       </c>
       <c r="I77">
         <v>0</v>
       </c>
       <c r="J77">
-        <v>0.59658132259999996</v>
+        <v>0.5965813226</v>
       </c>
       <c r="K77">
         <v>95</v>
@@ -4262,15 +4230,15 @@
         <v>5</v>
       </c>
       <c r="N77">
-        <v>1.5680369079999999E-3</v>
+        <v>0.001568036908</v>
       </c>
       <c r="P77">
-        <v>-1.5680369079999999E-3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001568036908</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
       <c r="A78">
-        <v>883.05011469999999</v>
+        <v>883.0501147</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -4279,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>39.624147020428403</v>
+        <v>39.6241470204284</v>
       </c>
       <c r="E78">
         <v>90</v>
@@ -4291,13 +4259,13 @@
         <v>5</v>
       </c>
       <c r="H78">
-        <v>98.378324469999995</v>
+        <v>98.37832447</v>
       </c>
       <c r="I78">
-        <v>1.1771123830000001</v>
+        <v>1.177112383</v>
       </c>
       <c r="J78">
-        <v>0.44456314829999999</v>
+        <v>0.4445631483</v>
       </c>
       <c r="K78">
         <v>90</v>
@@ -4309,18 +4277,18 @@
         <v>5</v>
       </c>
       <c r="N78">
-        <v>2.1135202979999999E-3</v>
+        <v>0.002113520298</v>
       </c>
       <c r="O78">
-        <v>-9.643545359E-4</v>
+        <v>-0.0009643545359</v>
       </c>
       <c r="P78">
-        <v>-1.1491657619999999E-3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001149165762</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
       <c r="A79">
-        <v>877.61026709999999</v>
+        <v>877.6102671</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -4329,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>44.709365400659301</v>
+        <v>44.7093654006593</v>
       </c>
       <c r="E79">
         <v>89</v>
@@ -4341,13 +4309,13 @@
         <v>6</v>
       </c>
       <c r="H79">
-        <v>98.350122470000002</v>
+        <v>98.35012247</v>
       </c>
       <c r="I79">
-        <v>1.1053458389999999</v>
+        <v>1.105345839</v>
       </c>
       <c r="J79">
-        <v>0.54453168649999995</v>
+        <v>0.5445316864999999</v>
       </c>
       <c r="K79">
         <v>89</v>
@@ -4359,18 +4327,18 @@
         <v>6</v>
       </c>
       <c r="N79">
-        <v>2.0901561579999999E-3</v>
+        <v>0.002090156158</v>
       </c>
       <c r="O79">
-        <v>-8.7061891830000004E-4</v>
+        <v>-0.0008706189183</v>
       </c>
       <c r="P79">
-        <v>-1.21953724E-3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.00121953724</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
       <c r="A80">
-        <v>872.01576899999998</v>
+        <v>872.015769</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -4379,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>50.033803617383199</v>
+        <v>50.0338036173832</v>
       </c>
       <c r="E80">
         <v>88</v>
@@ -4409,18 +4377,18 @@
         <v>7</v>
       </c>
       <c r="N80">
-        <v>2.060094359E-3</v>
+        <v>0.002060094359</v>
       </c>
       <c r="O80">
-        <v>-7.9154855410000003E-4</v>
+        <v>-0.0007915485541</v>
       </c>
       <c r="P80">
-        <v>-1.2685458050000001E-3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001268545805</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
       <c r="A81">
-        <v>866.26357499999995</v>
+        <v>866.2635749999999</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -4444,10 +4412,10 @@
         <v>98.27108011</v>
       </c>
       <c r="I81">
-        <v>0.97159766879999998</v>
+        <v>0.9715976688</v>
       </c>
       <c r="J81">
-        <v>0.75732222270000005</v>
+        <v>0.7573222227</v>
       </c>
       <c r="K81">
         <v>87</v>
@@ -4459,18 +4427,18 @@
         <v>8</v>
       </c>
       <c r="N81">
-        <v>2.0256050659999999E-3</v>
+        <v>0.002025605066</v>
       </c>
       <c r="O81">
-        <v>-7.239735E-4</v>
+        <v>-0.0007239735</v>
       </c>
       <c r="P81">
-        <v>-1.301631566E-3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001301631566</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
       <c r="A82">
-        <v>860.35143979999998</v>
+        <v>860.3514398</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -4479,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>61.403346149183299</v>
+        <v>61.4033461491833</v>
       </c>
       <c r="E82">
         <v>86</v>
@@ -4491,13 +4459,13 @@
         <v>9</v>
       </c>
       <c r="H82">
-        <v>98.220146880000001</v>
+        <v>98.22014688</v>
       </c>
       <c r="I82">
-        <v>0.90925595979999996</v>
+        <v>0.9092559598</v>
       </c>
       <c r="J82">
-        <v>0.87059716350000005</v>
+        <v>0.8705971635</v>
       </c>
       <c r="K82">
         <v>86</v>
@@ -4509,18 +4477,18 @@
         <v>9</v>
       </c>
       <c r="N82">
-        <v>1.9883322999999999E-3</v>
+        <v>0.0019883323</v>
       </c>
       <c r="O82">
-        <v>-6.6560484349999997E-4</v>
+        <v>-0.0006656048435</v>
       </c>
       <c r="P82">
-        <v>-1.322727456E-3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001322727456</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
       <c r="A83">
-        <v>854.27788369999996</v>
+        <v>854.2778837</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -4529,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>67.448760627974195</v>
+        <v>67.4487606279742</v>
       </c>
       <c r="E83">
         <v>85</v>
@@ -4541,13 +4509,13 @@
         <v>10</v>
       </c>
       <c r="H83">
-        <v>98.161505480000002</v>
+        <v>98.16150548</v>
       </c>
       <c r="I83">
         <v>0.8497310374</v>
       </c>
       <c r="J83">
-        <v>0.98876347880000004</v>
+        <v>0.9887634788</v>
       </c>
       <c r="K83">
         <v>85</v>
@@ -4559,18 +4527,18 @@
         <v>10</v>
       </c>
       <c r="N83">
-        <v>1.9495180039999999E-3</v>
+        <v>0.001949518004</v>
       </c>
       <c r="O83">
-        <v>-6.1475261540000004E-4</v>
+        <v>-0.0006147526154</v>
       </c>
       <c r="P83">
-        <v>-1.3347653890000001E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001334765389</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
       <c r="A84">
-        <v>902.95230500000002</v>
+        <v>902.952305</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -4579,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>21.119025008632399</v>
+        <v>21.1190250086324</v>
       </c>
       <c r="E84">
         <v>94</v>
@@ -4591,10 +4559,10 @@
         <v>0</v>
       </c>
       <c r="H84">
-        <v>98.088239540000004</v>
+        <v>98.08823954</v>
       </c>
       <c r="I84">
-        <v>1.9117604560000001</v>
+        <v>1.911760456</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4609,15 +4577,15 @@
         <v>0</v>
       </c>
       <c r="N84">
-        <v>1.9357860030000001E-3</v>
+        <v>0.001935786003</v>
       </c>
       <c r="O84">
-        <v>-1.9357860030000001E-3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001935786003</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
       <c r="A85">
-        <v>898.44933490000005</v>
+        <v>898.4493349000001</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -4626,7 +4594,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>24.889406791034499</v>
+        <v>24.8894067910345</v>
       </c>
       <c r="E85">
         <v>93</v>
@@ -4638,13 +4606,13 @@
         <v>1</v>
       </c>
       <c r="H85">
-        <v>98.123180739999995</v>
+        <v>98.12318074</v>
       </c>
       <c r="I85">
-        <v>1.7999778209999999</v>
+        <v>1.799977821</v>
       </c>
       <c r="J85">
-        <v>7.6841437499999998E-2</v>
+        <v>0.0768414375</v>
       </c>
       <c r="K85">
         <v>93</v>
@@ -4656,18 +4624,18 @@
         <v>1</v>
       </c>
       <c r="N85">
-        <v>2.0582215680000002E-3</v>
+        <v>0.002058221568</v>
       </c>
       <c r="O85">
-        <v>-1.68731863E-3</v>
+        <v>-0.00168731863</v>
       </c>
       <c r="P85">
-        <v>-3.7090293860000002E-4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0003709029386</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
       <c r="A86">
-        <v>893.81635510000001</v>
+        <v>893.8163551</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -4688,13 +4656,13 @@
         <v>2</v>
       </c>
       <c r="H86">
-        <v>98.149171100000004</v>
+        <v>98.1491711</v>
       </c>
       <c r="I86">
-        <v>1.6940493919999999</v>
+        <v>1.694049392</v>
       </c>
       <c r="J86">
-        <v>0.15677951130000001</v>
+        <v>0.1567795113</v>
       </c>
       <c r="K86">
         <v>92</v>
@@ -4706,18 +4674,18 @@
         <v>2</v>
       </c>
       <c r="N86">
-        <v>2.1327568849999999E-3</v>
+        <v>0.002132756885</v>
       </c>
       <c r="O86">
-        <v>-1.49343298E-3</v>
+        <v>-0.00149343298</v>
       </c>
       <c r="P86">
-        <v>-6.3932390509999996E-4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0006393239051</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
       <c r="A87">
-        <v>889.04581350000001</v>
+        <v>889.0458135</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -4726,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>32.956958997788703</v>
+        <v>32.9569589977887</v>
       </c>
       <c r="E87">
         <v>91</v>
@@ -4738,13 +4706,13 @@
         <v>3</v>
       </c>
       <c r="H87">
-        <v>98.166430449999993</v>
+        <v>98.16643044999999</v>
       </c>
       <c r="I87">
         <v>1.593543052</v>
       </c>
       <c r="J87">
-        <v>0.24002649470000001</v>
+        <v>0.2400264947</v>
       </c>
       <c r="K87">
         <v>91</v>
@@ -4756,18 +4724,18 @@
         <v>3</v>
       </c>
       <c r="N87">
-        <v>2.1739203480000001E-3</v>
+        <v>0.002173920348</v>
       </c>
       <c r="O87">
-        <v>-1.3366665749999999E-3</v>
+        <v>-0.001336666575</v>
       </c>
       <c r="P87">
-        <v>-8.3725377269999995E-4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0008372537726999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
       <c r="A88">
-        <v>896.73018079999997</v>
+        <v>896.7301808</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -4776,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>34.366947096820297</v>
+        <v>34.3669470968203</v>
       </c>
       <c r="E88">
         <v>94</v>
@@ -4788,13 +4756,13 @@
         <v>6</v>
       </c>
       <c r="H88">
-        <v>99.272784180000002</v>
+        <v>99.27278418</v>
       </c>
       <c r="I88">
         <v>0</v>
       </c>
       <c r="J88">
-        <v>0.72721582299999998</v>
+        <v>0.727215823</v>
       </c>
       <c r="K88">
         <v>94</v>
@@ -4806,15 +4774,15 @@
         <v>6</v>
       </c>
       <c r="N88">
-        <v>1.5336581470000001E-3</v>
+        <v>0.001533658147</v>
       </c>
       <c r="P88">
-        <v>-1.5336581470000001E-3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001533658147</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
       <c r="A89">
-        <v>884.13124579999999</v>
+        <v>884.1312458</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -4823,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>37.296936961945697</v>
+        <v>37.2969369619457</v>
       </c>
       <c r="E89">
         <v>90</v>
@@ -4835,13 +4803,13 @@
         <v>4</v>
       </c>
       <c r="H89">
-        <v>98.175134920000005</v>
+        <v>98.17513492</v>
       </c>
       <c r="I89">
         <v>1.49807205</v>
       </c>
       <c r="J89">
-        <v>0.32679303539999999</v>
+        <v>0.3267930354</v>
       </c>
       <c r="K89">
         <v>90</v>
@@ -4853,18 +4821,18 @@
         <v>4</v>
       </c>
       <c r="N89">
-        <v>2.1911126810000001E-3</v>
+        <v>0.002191112681</v>
       </c>
       <c r="O89">
-        <v>-1.2065982810000001E-3</v>
+        <v>-0.001206598281</v>
       </c>
       <c r="P89">
-        <v>-9.8451439920000001E-4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0009845143992</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
       <c r="A90">
-        <v>879.06721549999997</v>
+        <v>879.0672155</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -4873,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>41.861217730983299</v>
+        <v>41.8612177309833</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -4885,13 +4853,13 @@
         <v>5</v>
       </c>
       <c r="H90">
-        <v>98.175420149999994</v>
+        <v>98.17542014999999</v>
       </c>
       <c r="I90">
         <v>1.407291004</v>
       </c>
       <c r="J90">
-        <v>0.41728884389999998</v>
+        <v>0.4172888439</v>
       </c>
       <c r="K90">
         <v>89</v>
@@ -4903,18 +4871,18 @@
         <v>5</v>
       </c>
       <c r="N90">
-        <v>2.1908374889999999E-3</v>
+        <v>0.002190837489</v>
       </c>
       <c r="O90">
-        <v>-1.0966023759999999E-3</v>
+        <v>-0.001096602376</v>
       </c>
       <c r="P90">
-        <v>-1.094235113E-3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001094235113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
       <c r="A91">
-        <v>873.84925899999996</v>
+        <v>873.849259</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -4923,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>46.659219330326302</v>
+        <v>46.6592193303263</v>
       </c>
       <c r="E91">
         <v>88</v>
@@ -4938,7 +4906,7 @@
         <v>98.16738445</v>
       </c>
       <c r="I91">
-        <v>1.3208922400000001</v>
+        <v>1.32089224</v>
       </c>
       <c r="J91">
         <v>0.5117233082</v>
@@ -4953,18 +4921,18 @@
         <v>6</v>
       </c>
       <c r="N91">
-        <v>2.177798199E-3</v>
+        <v>0.002177798199</v>
       </c>
       <c r="O91">
-        <v>-1.002233793E-3</v>
+        <v>-0.001002233793</v>
       </c>
       <c r="P91">
-        <v>-1.1755644059999999E-3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001175564406</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
       <c r="A92">
-        <v>868.47383530000002</v>
+        <v>868.4738353</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -4985,13 +4953,13 @@
         <v>7</v>
       </c>
       <c r="H92">
-        <v>98.151091629999996</v>
+        <v>98.15109163</v>
       </c>
       <c r="I92">
-        <v>1.2386023390000001</v>
+        <v>1.238602339</v>
       </c>
       <c r="J92">
-        <v>0.61030603090000002</v>
+        <v>0.6103060309</v>
       </c>
       <c r="K92">
         <v>87</v>
@@ -5003,18 +4971,18 @@
         <v>7</v>
       </c>
       <c r="N92">
-        <v>2.1555380410000001E-3</v>
+        <v>0.002155538041</v>
       </c>
       <c r="O92">
-        <v>-9.2038966859999999E-4</v>
+        <v>-0.0009203896686</v>
       </c>
       <c r="P92">
-        <v>-1.235148372E-3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001235148372</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
       <c r="A93">
-        <v>862.93827850000002</v>
+        <v>862.9382785</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -5035,13 +5003,13 @@
         <v>8</v>
       </c>
       <c r="H93">
-        <v>98.126573669999999</v>
+        <v>98.12657367</v>
       </c>
       <c r="I93">
-        <v>1.1601790199999999</v>
+        <v>1.16017902</v>
       </c>
       <c r="J93">
-        <v>0.71324731180000001</v>
+        <v>0.7132473118</v>
       </c>
       <c r="K93">
         <v>86</v>
@@ -5053,18 +5021,18 @@
         <v>8</v>
       </c>
       <c r="N93">
-        <v>2.126726055E-3</v>
+        <v>0.002126726055</v>
       </c>
       <c r="O93">
-        <v>-8.4879512930000002E-4</v>
+        <v>-0.0008487951293</v>
       </c>
       <c r="P93">
-        <v>-1.277930926E-3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001277930926</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
       <c r="A94">
-        <v>857.24075449999998</v>
+        <v>857.2407545</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -5073,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>62.489124168401403</v>
+        <v>62.4891241684014</v>
       </c>
       <c r="E94">
         <v>85</v>
@@ -5085,13 +5053,13 @@
         <v>9</v>
       </c>
       <c r="H94">
-        <v>98.093833250000003</v>
+        <v>98.09383325</v>
       </c>
       <c r="I94">
-        <v>1.0854081900000001</v>
+        <v>1.08540819</v>
       </c>
       <c r="J94">
-        <v>0.82075856179999995</v>
+        <v>0.8207585618</v>
       </c>
       <c r="K94">
         <v>85</v>
@@ -5103,18 +5071,18 @@
         <v>9</v>
       </c>
       <c r="N94">
-        <v>2.093427241E-3</v>
+        <v>0.002093427241</v>
       </c>
       <c r="O94">
-        <v>-7.8574139019999998E-4</v>
+        <v>-0.0007857413902</v>
       </c>
       <c r="P94">
-        <v>-1.3076858509999999E-3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001307685851</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
       <c r="A95">
-        <v>851.38022030000002</v>
+        <v>851.3802203</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -5135,13 +5103,13 @@
         <v>10</v>
       </c>
       <c r="H95">
-        <v>98.052846130000006</v>
+        <v>98.05284613000001</v>
       </c>
       <c r="I95">
-        <v>1.0141012069999999</v>
+        <v>1.014101207</v>
       </c>
       <c r="J95">
-        <v>0.93305266109999996</v>
+        <v>0.9330526611</v>
       </c>
       <c r="K95">
         <v>84</v>
@@ -5153,16 +5121,16 @@
         <v>10</v>
       </c>
       <c r="N95">
-        <v>2.057238613E-3</v>
+        <v>0.002057238613</v>
       </c>
       <c r="O95">
-        <v>-7.2990401550000002E-4</v>
+        <v>-0.0007299040155</v>
       </c>
       <c r="P95">
-        <v>-1.3273345980000001E-3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001327334598</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
       <c r="A96">
         <v>897.7625726</v>
       </c>
@@ -5173,7 +5141,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>24.869284244994802</v>
+        <v>24.8692842449948</v>
       </c>
       <c r="E96">
         <v>93</v>
@@ -5185,10 +5153,10 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <v>97.769069459999997</v>
+        <v>97.76906946</v>
       </c>
       <c r="I96">
-        <v>2.2309305400000001</v>
+        <v>2.23093054</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5203,15 +5171,15 @@
         <v>0</v>
       </c>
       <c r="N96">
-        <v>1.9175133170000001E-3</v>
+        <v>0.001917513317</v>
       </c>
       <c r="O96">
-        <v>-1.9175133170000001E-3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001917513317</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
       <c r="A97">
-        <v>893.50529940000001</v>
+        <v>893.5052994</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -5220,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>28.350902133065599</v>
+        <v>28.3509021330656</v>
       </c>
       <c r="E97">
         <v>92</v>
@@ -5232,13 +5200,13 @@
         <v>1</v>
       </c>
       <c r="H97">
-        <v>97.829182829999993</v>
+        <v>97.82918282999999</v>
       </c>
       <c r="I97">
-        <v>2.0991957530000001</v>
+        <v>2.099195753</v>
       </c>
       <c r="J97">
-        <v>7.1621415760000001E-2</v>
+        <v>0.07162141576</v>
       </c>
       <c r="K97">
         <v>92</v>
@@ -5250,16 +5218,16 @@
         <v>1</v>
       </c>
       <c r="N97">
-        <v>2.055814096E-3</v>
+        <v>0.002055814096</v>
       </c>
       <c r="O97">
-        <v>-1.728374761E-3</v>
+        <v>-0.001728374761</v>
       </c>
       <c r="P97">
-        <v>-3.2743933530000001E-4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0003274393353</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
       <c r="A98">
         <v>889.1138899</v>
       </c>
@@ -5270,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>31.996510805784599</v>
+        <v>31.9965108057846</v>
       </c>
       <c r="E98">
         <v>91</v>
@@ -5282,13 +5250,13 @@
         <v>2</v>
       </c>
       <c r="H98">
-        <v>97.879121609999999</v>
+        <v>97.87912161</v>
       </c>
       <c r="I98">
         <v>1.974536378</v>
       </c>
       <c r="J98">
-        <v>0.14634200680000001</v>
+        <v>0.1463420068</v>
       </c>
       <c r="K98">
         <v>91</v>
@@ -5300,18 +5268,18 @@
         <v>2</v>
       </c>
       <c r="N98">
-        <v>2.1495105940000001E-3</v>
+        <v>0.002149510594</v>
       </c>
       <c r="O98">
-        <v>-1.5702755440000001E-3</v>
+        <v>-0.001570275544</v>
       </c>
       <c r="P98">
-        <v>-5.7923505059999999E-4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0005792350506</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99">
-        <v>890.13598590000004</v>
+        <v>890.1359859</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -5320,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>40.911500529169203</v>
+        <v>40.9115005291692</v>
       </c>
       <c r="E99">
         <v>93</v>
@@ -5332,7 +5300,7 @@
         <v>7</v>
       </c>
       <c r="H99">
-        <v>99.137604920000001</v>
+        <v>99.13760492</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -5350,15 +5318,15 @@
         <v>7</v>
       </c>
       <c r="N99">
-        <v>1.4994342060000001E-3</v>
+        <v>0.001499434206</v>
       </c>
       <c r="P99">
-        <v>-1.4994342060000001E-3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001499434206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100">
-        <v>884.58085430000006</v>
+        <v>884.5808543000001</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -5367,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>35.831915873242401</v>
+        <v>35.8319158732424</v>
       </c>
       <c r="E100">
         <v>90</v>
@@ -5379,13 +5347,13 @@
         <v>3</v>
       </c>
       <c r="H100">
-        <v>97.919219920000003</v>
+        <v>97.91921992</v>
       </c>
       <c r="I100">
-        <v>1.8564186970000001</v>
+        <v>1.856418697</v>
       </c>
       <c r="J100">
-        <v>0.22436138729999999</v>
+        <v>0.2243613873</v>
       </c>
       <c r="K100">
         <v>90</v>
@@ -5397,18 +5365,18 @@
         <v>3</v>
       </c>
       <c r="N100">
-        <v>2.2094415780000002E-3</v>
+        <v>0.002209441578</v>
       </c>
       <c r="O100">
-        <v>-1.4350246179999999E-3</v>
+        <v>-0.001435024618</v>
       </c>
       <c r="P100">
-        <v>-7.7441695949999995E-4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0007744169595</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
       <c r="A101">
-        <v>879.89986829999998</v>
+        <v>879.8998683</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -5417,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>39.877124951244802</v>
+        <v>39.8771249512448</v>
       </c>
       <c r="E101">
         <v>89</v>
@@ -5429,13 +5397,13 @@
         <v>4</v>
       </c>
       <c r="H101">
-        <v>97.949756620000002</v>
+        <v>97.94975662</v>
       </c>
       <c r="I101">
-        <v>1.7443659060000001</v>
+        <v>1.744365906</v>
       </c>
       <c r="J101">
-        <v>0.30587747570000001</v>
+        <v>0.3058774757</v>
       </c>
       <c r="K101">
         <v>89</v>
@@ -5447,18 +5415,18 @@
         <v>4</v>
       </c>
       <c r="N101">
-        <v>2.2434425100000001E-3</v>
+        <v>0.00224344251</v>
       </c>
       <c r="O101">
-        <v>-1.3174181160000001E-3</v>
+        <v>-0.001317418116</v>
       </c>
       <c r="P101">
-        <v>-9.2602439399999995E-4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.000926024394</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102">
-        <v>875.06570180000006</v>
+        <v>875.0657018000001</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -5467,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>44.146837432514701</v>
+        <v>44.1468374325147</v>
       </c>
       <c r="E102">
         <v>88</v>
@@ -5479,13 +5447,13 @@
         <v>5</v>
       </c>
       <c r="H102">
-        <v>97.970960009999999</v>
+        <v>97.97096001</v>
       </c>
       <c r="I102">
         <v>1.637952868</v>
       </c>
       <c r="J102">
-        <v>0.39108712439999999</v>
+        <v>0.3910871244</v>
       </c>
       <c r="K102">
         <v>88</v>
@@ -5497,18 +5465,18 @@
         <v>5</v>
       </c>
       <c r="N102">
-        <v>2.2574485909999998E-3</v>
+        <v>0.002257448591</v>
       </c>
       <c r="O102">
-        <v>-1.2139692009999999E-3</v>
+        <v>-0.001213969201</v>
       </c>
       <c r="P102">
-        <v>-1.0434793899999999E-3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.00104347939</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
       <c r="A103">
-        <v>870.07415330000003</v>
+        <v>870.0741533</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -5517,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>48.650882982037302</v>
+        <v>48.6508829820373</v>
       </c>
       <c r="E103">
         <v>87</v>
@@ -5529,13 +5497,13 @@
         <v>6</v>
       </c>
       <c r="H103">
-        <v>97.983012059999993</v>
+        <v>97.98301205999999</v>
       </c>
       <c r="I103">
-        <v>1.5368012660000001</v>
+        <v>1.536801266</v>
       </c>
       <c r="J103">
-        <v>0.48018667250000002</v>
+        <v>0.4801866725</v>
       </c>
       <c r="K103">
         <v>87</v>
@@ -5547,18 +5515,18 @@
         <v>6</v>
       </c>
       <c r="N103">
-        <v>2.256134949E-3</v>
+        <v>0.002256134949</v>
       </c>
       <c r="O103">
-        <v>-1.1222460599999999E-3</v>
+        <v>-0.00112224606</v>
       </c>
       <c r="P103">
-        <v>-1.1338888889999999E-3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001133888889</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104">
-        <v>864.92199040000003</v>
+        <v>864.9219904</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -5567,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>53.394618247349896</v>
+        <v>53.3946182473499</v>
       </c>
       <c r="E104">
         <v>86</v>
@@ -5579,13 +5547,13 @@
         <v>7</v>
       </c>
       <c r="H104">
-        <v>97.986052419999993</v>
+        <v>97.98605241999999</v>
       </c>
       <c r="I104">
         <v>1.440575156</v>
       </c>
       <c r="J104">
-        <v>0.57337242929999999</v>
+        <v>0.5733724293</v>
       </c>
       <c r="K104">
         <v>86</v>
@@ -5597,18 +5565,18 @@
         <v>7</v>
       </c>
       <c r="N104">
-        <v>2.2431848370000002E-3</v>
+        <v>0.002243184837</v>
       </c>
       <c r="O104">
-        <v>-1.0404409689999999E-3</v>
+        <v>-0.001040440969</v>
       </c>
       <c r="P104">
-        <v>-1.202743868E-3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001202743868</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
       <c r="A105">
-        <v>859.60689439999999</v>
+        <v>859.6068944</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -5617,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>58.379327973050898</v>
+        <v>58.3793279730509</v>
       </c>
       <c r="E105">
         <v>85</v>
@@ -5629,13 +5597,13 @@
         <v>8</v>
       </c>
       <c r="H105">
-        <v>97.980182040000003</v>
+        <v>97.98018204</v>
       </c>
       <c r="I105">
-        <v>1.3489768630000001</v>
+        <v>1.348976863</v>
       </c>
       <c r="J105">
-        <v>0.67084109449999996</v>
+        <v>0.6708410945</v>
       </c>
       <c r="K105">
         <v>85</v>
@@ -5647,18 +5615,18 @@
         <v>8</v>
       </c>
       <c r="N105">
-        <v>2.22156282E-3</v>
+        <v>0.00222156282</v>
       </c>
       <c r="O105">
-        <v>-9.6717409660000003E-4</v>
+        <v>-0.0009671740966</v>
       </c>
       <c r="P105">
-        <v>-1.2543887230000001E-3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001254388723</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
       <c r="A106">
-        <v>854.12741010000002</v>
+        <v>854.1274101</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -5667,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>63.608963137649802</v>
+        <v>63.6089631376498</v>
       </c>
       <c r="E106">
         <v>84</v>
@@ -5679,13 +5647,13 @@
         <v>9</v>
       </c>
       <c r="H106">
-        <v>97.965466669999998</v>
+        <v>97.96546667</v>
       </c>
       <c r="I106">
-        <v>1.2617432120000001</v>
+        <v>1.261743212</v>
       </c>
       <c r="J106">
-        <v>0.77279011669999997</v>
+        <v>0.7727901167</v>
       </c>
       <c r="K106">
         <v>84</v>
@@ -5697,18 +5665,18 @@
         <v>9</v>
       </c>
       <c r="N106">
-        <v>2.1936507239999998E-3</v>
+        <v>0.002193650724</v>
       </c>
       <c r="O106">
-        <v>-9.0134836450000001E-4</v>
+        <v>-0.0009013483645</v>
       </c>
       <c r="P106">
-        <v>-1.29230236E-3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.00129230236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
       <c r="A107">
-        <v>848.48289820000002</v>
+        <v>848.4828982</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -5717,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>69.065299629478005</v>
+        <v>69.06529962947801</v>
       </c>
       <c r="E107">
         <v>83</v>
@@ -5729,13 +5697,13 @@
         <v>10</v>
       </c>
       <c r="H107">
-        <v>97.941939989999995</v>
+        <v>97.94193998999999</v>
       </c>
       <c r="I107">
-        <v>1.1786420209999999</v>
+        <v>1.178642021</v>
       </c>
       <c r="J107">
-        <v>0.87941799350000005</v>
+        <v>0.8794179935000001</v>
       </c>
       <c r="K107">
         <v>83</v>
@@ -5747,18 +5715,18 @@
         <v>10</v>
       </c>
       <c r="N107">
-        <v>2.1613548839999998E-3</v>
+        <v>0.002161354884</v>
       </c>
       <c r="O107">
-        <v>-8.4206349389999999E-4</v>
+        <v>-0.0008420634939</v>
       </c>
       <c r="P107">
-        <v>-1.31929139E-3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.00131929139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
       <c r="A108">
-        <v>892.51953839999999</v>
+        <v>892.5195384</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -5767,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>28.715981187904099</v>
+        <v>28.7159811879041</v>
       </c>
       <c r="E108">
         <v>92</v>
@@ -5779,10 +5747,10 @@
         <v>0</v>
       </c>
       <c r="H108">
-        <v>97.447187189999994</v>
+        <v>97.44718718999999</v>
       </c>
       <c r="I108">
-        <v>2.5528128080000001</v>
+        <v>2.552812808</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5797,15 +5765,15 @@
         <v>0</v>
       </c>
       <c r="N108">
-        <v>1.896671102E-3</v>
+        <v>0.001896671102</v>
       </c>
       <c r="O108">
-        <v>-1.896671102E-3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001896671102</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
       <c r="A109">
-        <v>888.51267010000004</v>
+        <v>888.5126701</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -5814,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>31.904899067357299</v>
+        <v>31.9048990673573</v>
       </c>
       <c r="E109">
         <v>91</v>
@@ -5826,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="H109">
-        <v>97.532631330000001</v>
+        <v>97.53263133</v>
       </c>
       <c r="I109">
-        <v>2.4007358139999999</v>
+        <v>2.400735814</v>
       </c>
       <c r="J109">
-        <v>6.6632859380000006E-2</v>
+        <v>0.06663285938000001</v>
       </c>
       <c r="K109">
         <v>91</v>
@@ -5844,16 +5812,16 @@
         <v>1</v>
       </c>
       <c r="N109">
-        <v>2.047157852E-3</v>
+        <v>0.002047157852</v>
       </c>
       <c r="O109">
-        <v>-1.7546458879999999E-3</v>
+        <v>-0.001754645888</v>
       </c>
       <c r="P109">
-        <v>-2.925119636E-4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0002925119636</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
       <c r="A110">
         <v>883.3902994</v>
       </c>
@@ -5864,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>47.715058755151297</v>
+        <v>47.7150587551513</v>
       </c>
       <c r="E110">
         <v>92</v>
@@ -5876,7 +5844,7 @@
         <v>8</v>
       </c>
       <c r="H110">
-        <v>98.997544239999996</v>
+        <v>98.99754424</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -5894,15 +5862,15 @@
         <v>8</v>
       </c>
       <c r="N110">
-        <v>1.465579654E-3</v>
+        <v>0.001465579654</v>
       </c>
       <c r="P110">
-        <v>-1.465579654E-3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001465579654</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
       <c r="A111">
-        <v>884.36739490000002</v>
+        <v>884.3673949</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -5911,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>35.253910735530603</v>
+        <v>35.2539107355306</v>
       </c>
       <c r="E111">
         <v>90</v>
@@ -5926,7 +5894,7 @@
         <v>97.60662078</v>
       </c>
       <c r="I111">
-        <v>2.2570217260000001</v>
+        <v>2.257021726</v>
       </c>
       <c r="J111">
         <v>0.13635749</v>
@@ -5941,18 +5909,18 @@
         <v>2</v>
       </c>
       <c r="N111">
-        <v>2.1571178640000001E-3</v>
+        <v>0.002157117864</v>
       </c>
       <c r="O111">
-        <v>-1.6285959070000001E-3</v>
+        <v>-0.001628595907</v>
       </c>
       <c r="P111">
-        <v>-5.2852195709999995E-4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0005285219571</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
       <c r="A112">
-        <v>880.07624720000001</v>
+        <v>880.0762472</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -5961,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>38.790860287606101</v>
+        <v>38.7908602876061</v>
       </c>
       <c r="E112">
         <v>89</v>
@@ -5973,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="H112">
-        <v>97.669611720000006</v>
+        <v>97.66961172000001</v>
       </c>
       <c r="I112">
-        <v>2.1210258820000001</v>
+        <v>2.121025882</v>
       </c>
       <c r="J112">
-        <v>0.20936239840000001</v>
+        <v>0.2093623984</v>
       </c>
       <c r="K112">
         <v>89</v>
@@ -5991,18 +5959,18 @@
         <v>3</v>
       </c>
       <c r="N112">
-        <v>2.234204999E-3</v>
+        <v>0.002234204999</v>
       </c>
       <c r="O112">
-        <v>-1.5150228849999999E-3</v>
+        <v>-0.001515022885</v>
       </c>
       <c r="P112">
-        <v>-7.191821142E-4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0007191821142</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
       <c r="A113">
-        <v>875.63300800000002</v>
+        <v>875.633008</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -6011,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>42.537217991924798</v>
+        <v>42.5372179919248</v>
       </c>
       <c r="E113">
         <v>88</v>
@@ -6023,13 +5991,13 @@
         <v>4</v>
       </c>
       <c r="H113">
-        <v>97.721992220000004</v>
+        <v>97.72199222</v>
       </c>
       <c r="I113">
-        <v>1.9921734600000001</v>
+        <v>1.99217346</v>
       </c>
       <c r="J113">
-        <v>0.28583432440000001</v>
+        <v>0.2858343244</v>
       </c>
       <c r="K113">
         <v>88</v>
@@ -6041,18 +6009,18 @@
         <v>4</v>
       </c>
       <c r="N113">
-        <v>2.284524666E-3</v>
+        <v>0.002284524666</v>
       </c>
       <c r="O113">
-        <v>-1.411734752E-3</v>
+        <v>-0.001411734752</v>
       </c>
       <c r="P113">
-        <v>-8.7278991400000004E-4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.000872789914</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
       <c r="A114">
-        <v>871.03262129999996</v>
+        <v>871.0326213</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -6061,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>46.508673142796901</v>
+        <v>46.5086731427969</v>
       </c>
       <c r="E114">
         <v>87</v>
@@ -6073,13 +6041,13 @@
         <v>5</v>
       </c>
       <c r="H114">
-        <v>97.764088369999996</v>
+        <v>97.76408837</v>
       </c>
       <c r="I114">
-        <v>1.8699528089999999</v>
+        <v>1.869952809</v>
       </c>
       <c r="J114">
-        <v>0.36595882349999997</v>
+        <v>0.3659588235</v>
       </c>
       <c r="K114">
         <v>87</v>
@@ -6091,18 +6059,18 @@
         <v>5</v>
       </c>
       <c r="N114">
-        <v>2.3131872880000001E-3</v>
+        <v>0.002313187288</v>
       </c>
       <c r="O114">
-        <v>-1.3173270429999999E-3</v>
+        <v>-0.001317327043</v>
       </c>
       <c r="P114">
-        <v>-9.9586024480000004E-4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.0009958602448</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
       <c r="A115">
-        <v>866.27111730000001</v>
+        <v>866.2711173</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -6111,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>50.715646479823398</v>
+        <v>50.7156464798234</v>
       </c>
       <c r="E115">
         <v>86</v>
@@ -6123,13 +6091,13 @@
         <v>6</v>
       </c>
       <c r="H115">
-        <v>97.796170140000001</v>
+        <v>97.79617014</v>
       </c>
       <c r="I115">
-        <v>1.7539091019999999</v>
+        <v>1.753909102</v>
       </c>
       <c r="J115">
-        <v>0.44992075850000002</v>
+        <v>0.4499207585</v>
       </c>
       <c r="K115">
         <v>86</v>
@@ -6141,16 +6109,16 @@
         <v>6</v>
       </c>
       <c r="N115">
-        <v>2.3244576269999999E-3</v>
+        <v>0.002324457627</v>
       </c>
       <c r="O115">
-        <v>-1.2307966210000001E-3</v>
+        <v>-0.001230796621</v>
       </c>
       <c r="P115">
-        <v>-1.0936610070000001E-3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001093661007</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
       <c r="A116">
         <v>861.3455424</v>
       </c>
@@ -6161,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>55.163770434578502</v>
+        <v>55.1637704345785</v>
       </c>
       <c r="E116">
         <v>85</v>
@@ -6173,10 +6141,10 @@
         <v>7</v>
       </c>
       <c r="H116">
-        <v>97.818456409999996</v>
+        <v>97.81845641</v>
       </c>
       <c r="I116">
-        <v>1.6436388449999999</v>
+        <v>1.643638845</v>
       </c>
       <c r="J116">
         <v>0.5379047441</v>
@@ -6191,18 +6159,18 @@
         <v>7</v>
       </c>
       <c r="N116">
-        <v>2.3219737610000002E-3</v>
+        <v>0.002321973761</v>
       </c>
       <c r="O116">
-        <v>-1.15140632E-3</v>
+        <v>-0.00115140632</v>
       </c>
       <c r="P116">
-        <v>-1.1705674409999999E-3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001170567441</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
       <c r="A117">
-        <v>856.25389629999995</v>
+        <v>856.2538963</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -6211,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>59.854572354416199</v>
+        <v>59.8545723544162</v>
       </c>
       <c r="E117">
         <v>84</v>
@@ -6223,13 +6191,13 @@
         <v>8</v>
       </c>
       <c r="H117">
-        <v>97.831119869999995</v>
+        <v>97.83111986999999</v>
       </c>
       <c r="I117">
-        <v>1.5387846199999999</v>
+        <v>1.53878462</v>
       </c>
       <c r="J117">
-        <v>0.63009551139999997</v>
+        <v>0.6300955114</v>
       </c>
       <c r="K117">
         <v>84</v>
@@ -6241,18 +6209,18 @@
         <v>8</v>
       </c>
       <c r="N117">
-        <v>2.3087992660000001E-3</v>
+        <v>0.002308799266</v>
       </c>
       <c r="O117">
-        <v>-1.078555476E-3</v>
+        <v>-0.001078555476</v>
       </c>
       <c r="P117">
-        <v>-1.2302437900000001E-3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.00123024379</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
       <c r="A118">
-        <v>850.99507270000004</v>
+        <v>850.9950727</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -6261,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>64.791265923874803</v>
+        <v>64.7912659238748</v>
       </c>
       <c r="E118">
         <v>83</v>
@@ -6273,13 +6241,13 @@
         <v>9</v>
       </c>
       <c r="H118">
-        <v>97.834291390000004</v>
+        <v>97.83429139</v>
       </c>
       <c r="I118">
-        <v>1.4390303870000001</v>
+        <v>1.439030387</v>
       </c>
       <c r="J118">
-        <v>0.72667822309999996</v>
+        <v>0.7266782231</v>
       </c>
       <c r="K118">
         <v>83</v>
@@ -6291,18 +6259,18 @@
         <v>9</v>
       </c>
       <c r="N118">
-        <v>2.2875546840000001E-3</v>
+        <v>0.002287554684</v>
       </c>
       <c r="O118">
-        <v>-1.011749481E-3</v>
+        <v>-0.001011749481</v>
       </c>
       <c r="P118">
-        <v>-1.2758052029999999E-3</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001275805203</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
       <c r="A119">
-        <v>845.56880690000003</v>
+        <v>845.5688069</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -6311,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>69.955606685331404</v>
+        <v>69.9556066853314</v>
       </c>
       <c r="E119">
         <v>82</v>
@@ -6323,13 +6291,13 @@
         <v>10</v>
       </c>
       <c r="H119">
-        <v>97.828064190000006</v>
+        <v>97.82806419000001</v>
       </c>
       <c r="I119">
-        <v>1.3440970889999999</v>
+        <v>1.344097089</v>
       </c>
       <c r="J119">
-        <v>0.82783871890000005</v>
+        <v>0.8278387189</v>
       </c>
       <c r="K119">
         <v>82</v>
@@ -6341,18 +6309,18 @@
         <v>10</v>
       </c>
       <c r="N119">
-        <v>2.2603483849999999E-3</v>
+        <v>0.002260348385</v>
       </c>
       <c r="O119">
-        <v>-9.5050755700000001E-4</v>
+        <v>-0.000950507557</v>
       </c>
       <c r="P119">
-        <v>-1.309840828E-3</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001309840828</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
       <c r="A120">
-        <v>887.21537190000004</v>
+        <v>887.2153719</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -6373,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="H120">
-        <v>97.121687370000004</v>
+        <v>97.12168737</v>
       </c>
       <c r="I120">
-        <v>2.8783126349999999</v>
+        <v>2.878312635</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6391,15 +6359,15 @@
         <v>0</v>
       </c>
       <c r="N120">
-        <v>1.8736134410000001E-3</v>
+        <v>0.001873613441</v>
       </c>
       <c r="O120">
-        <v>-1.8736134410000001E-3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001873613441</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
       <c r="A121">
-        <v>876.48820209999997</v>
+        <v>876.4882021</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -6420,13 +6388,13 @@
         <v>9</v>
       </c>
       <c r="H121">
-        <v>98.852260509999994</v>
+        <v>98.85226050999999</v>
       </c>
       <c r="I121">
         <v>0</v>
       </c>
       <c r="J121">
-        <v>1.1477394889999999</v>
+        <v>1.147739489</v>
       </c>
       <c r="K121">
         <v>91</v>
@@ -6438,13 +6406,13 @@
         <v>9</v>
       </c>
       <c r="N121">
-        <v>1.432275874E-3</v>
+        <v>0.001432275874</v>
       </c>
       <c r="P121">
-        <v>-1.432275874E-3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.15">
+        <v>-0.001432275874</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
       <c r="A122">
         <v>933.471</v>
       </c>
@@ -6455,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>2.01672000000599E-2</v>
+        <v>0.0201672000000599</v>
       </c>
       <c r="E122">
         <v>100</v>
@@ -6489,7 +6457,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>